--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_120/per_file_predictions_epoch_120.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_120/per_file_predictions_epoch_120.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="489">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="482">
   <si>
     <t>Filename</t>
   </si>
@@ -808,679 +808,658 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0.9594,0.0122,0.0071,0.0011</t>
+    <t>0,1,0,1</t>
+  </si>
+  <si>
+    <t>0.9827,0.0033,0.0035,0.0006</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.9216,0.0006,0.0007,0.0559</t>
+  </si>
+  <si>
+    <t>0.0044,0.0000,0.0005,0.9977</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9997,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.6105,0.0051,0.2821,0.0012</t>
+  </si>
+  <si>
+    <t>0.2108,0.0080,0.7600,0.0005</t>
+  </si>
+  <si>
+    <t>0.0176,0.0068,0.9784,0.0001</t>
+  </si>
+  <si>
+    <t>0.0090,0.0001,0.9904,0.0005</t>
+  </si>
+  <si>
+    <t>0.9922,0.0007,0.0029,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0009,0.9977,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.0364,0.9737,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.2232,0.0003,0.7144,0.0027</t>
+  </si>
+  <si>
+    <t>0.0169,0.0012,0.9651,0.0022</t>
+  </si>
+  <si>
+    <t>0.0003,0.0000,0.9993,0.0003</t>
+  </si>
+  <si>
+    <t>0.0009,0.0002,0.9981,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0000,0.9995,0.0001</t>
+  </si>
+  <si>
+    <t>0.1401,0.8993,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9427,0.0560,0.0047,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0005,0.9997,0.0015</t>
+  </si>
+  <si>
+    <t>0.0003,0.9995,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9946,0.0032,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.0041,0.9940,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9994,0.0058,0.0000</t>
+  </si>
+  <si>
+    <t>0.0090,0.9601,0.0150,0.0007</t>
+  </si>
+  <si>
+    <t>0.0014,0.0003,0.9962,0.0002</t>
+  </si>
+  <si>
+    <t>0.0146,0.0037,0.9607,0.0028</t>
+  </si>
+  <si>
+    <t>0.0011,0.0004,0.9959,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.0001,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9996,0.0006</t>
+  </si>
+  <si>
+    <t>0.0006,0.6455,0.0006,0.9911</t>
+  </si>
+  <si>
+    <t>0.0001,0.9993,0.0000,0.0013</t>
+  </si>
+  <si>
+    <t>0.0001,0.9995,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.9998,0.0002</t>
+  </si>
+  <si>
+    <t>0.0005,0.0000,0.9996,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0003,1.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9979,0.0019,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9941,0.0012,0.0022,0.0008</t>
+  </si>
+  <si>
+    <t>0.0001,0.0022,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0003,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9942,0.0051,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.8495,0.9982,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.0007,0.9989,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.9963,0.9991,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0021,0.9965,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.9968,0.0002,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.0285,0.0009,0.9751,0.0004</t>
+  </si>
+  <si>
+    <t>0.0002,0.0113,0.9992,0.0012</t>
+  </si>
+  <si>
+    <t>0.0000,0.9937,0.9983,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9285,0.9523,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.8748,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9881,0.9843,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0002,0.9998</t>
   </si>
   <si>
     <t>0.0000,0.0001,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.9746,0.0002,0.0002,0.0217</t>
-  </si>
-  <si>
-    <t>0.0013,0.0000,0.0000,0.9996</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9282,0.0090,0.0300,0.0008</t>
-  </si>
-  <si>
-    <t>0.2119,0.0018,0.8190,0.0007</t>
-  </si>
-  <si>
-    <t>0.4773,0.0007,0.6726,0.0001</t>
-  </si>
-  <si>
-    <t>0.0283,0.0002,0.9786,0.0003</t>
-  </si>
-  <si>
-    <t>0.9756,0.0006,0.0104,0.0008</t>
+    <t>0.0000,0.0001,0.0006,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.0000,0.0011,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0000,0.9984,0.9461,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9990,0.9984,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9609,0.9929,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9536,0.9974,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9547,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9938,0.9638,0.0000</t>
+  </si>
+  <si>
+    <t>0.9999,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0000,0.0002</t>
+  </si>
+  <si>
+    <t>0.9955,0.0026,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.9990,0.0004,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0004,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9987,0.0016,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9985,0.0013,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0002,0.9997,0.0001</t>
+  </si>
+  <si>
+    <t>0.0045,0.0015,0.9919,0.0002</t>
+  </si>
+  <si>
+    <t>0.9946,0.0002,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.0147,0.0001,0.9888,0.0002</t>
+  </si>
+  <si>
+    <t>0.0012,0.9970,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0001,0.0001</t>
   </si>
   <si>
     <t>0.0000,1.0000,0.0001,0.0000</t>
   </si>
   <si>
-    <t>0.0002,0.9995,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0194,0.9824,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9996,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.9996,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9349,0.0005,0.0343,0.0025</t>
-  </si>
-  <si>
-    <t>0.6203,0.0001,0.2643,0.0025</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.9993,0.0004</t>
-  </si>
-  <si>
-    <t>0.0048,0.0001,0.9949,0.0002</t>
-  </si>
-  <si>
-    <t>0.2252,0.0000,0.9134,0.0000</t>
-  </si>
-  <si>
-    <t>0.0012,0.0000,0.9984,0.0001</t>
-  </si>
-  <si>
-    <t>0.0031,0.0000,0.9974,0.0002</t>
-  </si>
-  <si>
-    <t>0.9187,0.0835,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.6166,0.4100,0.0105,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0006,0.9996,0.0015</t>
-  </si>
-  <si>
-    <t>0.0005,0.9973,0.0059,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9166,0.0028,0.0537,0.0008</t>
-  </si>
-  <si>
-    <t>0.1123,0.9031,0.0007,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.9948,0.1080,0.0000</t>
-  </si>
-  <si>
-    <t>0.0069,0.9126,0.0442,0.0015</t>
-  </si>
-  <si>
-    <t>0.0008,0.0102,0.9952,0.0005</t>
-  </si>
-  <si>
-    <t>0.0355,0.0056,0.9329,0.0012</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9989,0.0007</t>
-  </si>
-  <si>
-    <t>0.0006,0.0199,0.9983,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0003,0.9989,0.0030</t>
-  </si>
-  <si>
-    <t>0.0048,0.3309,0.0005,0.9737</t>
-  </si>
-  <si>
-    <t>0.0002,0.9989,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.0005,0.9989,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.9991,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.0001,0.0006,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9991,0.0040</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.9996,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9998,0.0005</t>
-  </si>
-  <si>
-    <t>0.9998,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9976,0.0008,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9947,0.0013,0.0019,0.0005</t>
-  </si>
-  <si>
-    <t>0.0001,0.0016,0.9999,0.0004</t>
-  </si>
-  <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9959,0.0039,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.9824,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0008,0.9977,0.0011</t>
-  </si>
-  <si>
-    <t>0.0000,0.9996,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.9989,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9993,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.8168,0.0005,0.2023,0.0002</t>
-  </si>
-  <si>
-    <t>0.1641,0.0004,0.8985,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0010,0.9997,0.0006</t>
-  </si>
-  <si>
-    <t>0.0000,0.9988,0.9661,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9492,0.9958,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.6833,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9964,0.9987,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0113,0.9996</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0001,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9982,0.9753,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9925,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9942,0.9815,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9969,0.9836,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9963,0.9982,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9980,0.5151,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9977,0.0028,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9998,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9971,0.0016,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9950,0.0031,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9990,0.0012,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9993,0.0004,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0130,0.0007,0.9929,0.0001</t>
-  </si>
-  <si>
-    <t>0.0060,0.0009,0.9903,0.0003</t>
-  </si>
-  <si>
-    <t>0.9779,0.0003,0.0080,0.0012</t>
-  </si>
-  <si>
-    <t>0.0038,0.0002,0.9958,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.9984,0.0008,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9999,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0698,0.9383,0.0015,0.0002</t>
-  </si>
-  <si>
-    <t>0.8292,0.0014,0.1153,0.0021</t>
-  </si>
-  <si>
-    <t>0.0779,0.0001,0.9302,0.0004</t>
-  </si>
-  <si>
-    <t>0.8410,0.0076,0.0524,0.0070</t>
-  </si>
-  <si>
-    <t>0.2588,0.0015,0.7024,0.0042</t>
-  </si>
-  <si>
-    <t>0.0006,0.1728,0.0003,0.9940</t>
-  </si>
-  <si>
-    <t>0.0005,0.9985,0.0014,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9995,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0011</t>
-  </si>
-  <si>
-    <t>0.0000,0.9964,0.9826,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.3432,0.7425,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9440,0.0409,0.0082,0.0007</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9991,0.0000,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9990,0.0000,0.0003,0.0003</t>
+    <t>0.3443,0.7100,0.0008,0.0002</t>
+  </si>
+  <si>
+    <t>0.1681,0.0037,0.7149,0.0043</t>
+  </si>
+  <si>
+    <t>0.8303,0.0003,0.1808,0.0003</t>
+  </si>
+  <si>
+    <t>0.9498,0.0011,0.0190,0.0034</t>
+  </si>
+  <si>
+    <t>0.6548,0.0058,0.1444,0.0129</t>
+  </si>
+  <si>
+    <t>0.0030,0.0254,0.0007,0.9944</t>
+  </si>
+  <si>
+    <t>0.0004,0.9983,0.0037,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0002,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9955,0.9939,0.0000</t>
+  </si>
+  <si>
+    <t>0.0808,0.9358,0.0006,0.0001</t>
+  </si>
+  <si>
+    <t>0.9375,0.0850,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0003,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0001,0.0001</t>
   </si>
   <si>
     <t>0.9997,0.0000,0.0000,0.0001</t>
   </si>
   <si>
-    <t>0.9989,0.0002,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0000,0.0005</t>
+    <t>0.9989,0.0002,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9993,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9994,0.0000,0.0000,0.0003</t>
+  </si>
+  <si>
+    <t>0.9990,0.0000,0.0001,0.0005</t>
+  </si>
+  <si>
+    <t>0.0000,0.1363,0.9991,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.5495,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0014,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0008,0.0003,0.9980,0.0001</t>
   </si>
   <si>
     <t>0.9997,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0000,0.0514,0.9994,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.8260,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0135,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0006,0.9980,0.0001</t>
-  </si>
-  <si>
-    <t>0.9985,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.6751,0.0002,0.2322,0.0024</t>
-  </si>
-  <si>
-    <t>0.8930,0.0001,0.1470,0.0001</t>
-  </si>
-  <si>
-    <t>0.9546,0.0006,0.0182,0.0036</t>
-  </si>
-  <si>
-    <t>0.0067,0.0000,0.0000,0.9989</t>
-  </si>
-  <si>
-    <t>0.0000,0.9877,0.9621,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.9983,0.0002,0.0005</t>
-  </si>
-  <si>
-    <t>0.9999,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9277,0.0995,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.9985,0.0001,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.7086,0.0001,0.0001,0.4546</t>
-  </si>
-  <si>
-    <t>0.0005,0.0013,0.9987,0.0009</t>
-  </si>
-  <si>
-    <t>0.9977,0.0000,0.0008,0.0003</t>
-  </si>
-  <si>
-    <t>0.9958,0.0002,0.0012,0.0005</t>
-  </si>
-  <si>
-    <t>0.2009,0.8422,0.0015,0.0001</t>
-  </si>
-  <si>
-    <t>0.9978,0.0002,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9888,0.0022,0.0029,0.0003</t>
-  </si>
-  <si>
-    <t>0.3636,0.1493,0.0751,0.0039</t>
-  </si>
-  <si>
-    <t>0.9228,0.0076,0.0396,0.0004</t>
-  </si>
-  <si>
-    <t>0.9977,0.0004,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9982,0.0007,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9986,0.0003,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0001,0.0001</t>
+    <t>0.1533,0.0019,0.8658,0.0004</t>
+  </si>
+  <si>
+    <t>0.0417,0.0002,0.9721,0.0001</t>
+  </si>
+  <si>
+    <t>0.7725,0.0013,0.1507,0.0079</t>
+  </si>
+  <si>
+    <t>0.0011,0.0001,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.0000,0.9974,0.8038,0.0000</t>
+  </si>
+  <si>
+    <t>0.0166,0.9765,0.0009,0.0034</t>
+  </si>
+  <si>
+    <t>0.2765,0.8197,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.9935,0.0000,0.0045,0.0002</t>
+  </si>
+  <si>
+    <t>0.5810,0.0001,0.0063,0.3333</t>
+  </si>
+  <si>
+    <t>0.0003,0.0009,0.9987,0.0041</t>
+  </si>
+  <si>
+    <t>0.9935,0.0000,0.0023,0.0011</t>
+  </si>
+  <si>
+    <t>0.9992,0.0000,0.0003,0.0002</t>
+  </si>
+  <si>
+    <t>0.0542,0.9372,0.0065,0.0001</t>
+  </si>
+  <si>
+    <t>0.9826,0.0056,0.0024,0.0006</t>
+  </si>
+  <si>
+    <t>0.4259,0.0437,0.0972,0.0051</t>
+  </si>
+  <si>
+    <t>0.7167,0.0911,0.0814,0.0007</t>
+  </si>
+  <si>
+    <t>0.9945,0.0007,0.0009,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0002,0.0001,0.0001</t>
   </si>
   <si>
     <t>0.9997,0.0000,0.0001,0.0001</t>
   </si>
   <si>
-    <t>0.9914,0.0023,0.0013,0.0025</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9705,0.0270,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.4999,0.6522,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9462,0.0696,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9899,0.0019,0.0043,0.0004</t>
-  </si>
-  <si>
-    <t>0.9261,0.1194,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0001,0.0002</t>
-  </si>
-  <si>
-    <t>0.9992,0.0009,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9839,0.0097,0.0038,0.0007</t>
-  </si>
-  <si>
-    <t>0.0009,0.0001,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.9845,0.0109,0.0033,0.0004</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0035,0.0053,0.9833,0.0044</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0711,0.9938,0.0002</t>
-  </si>
-  <si>
-    <t>0.0000,0.0002,1.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0000,1.0000,0.0000</t>
+    <t>0.9983,0.0002,0.0005,0.0002</t>
+  </si>
+  <si>
+    <t>0.9980,0.0003,0.0004,0.0004</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0001,0.0004</t>
+  </si>
+  <si>
+    <t>0.9956,0.0032,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.8770,0.1816,0.0008,0.0000</t>
+  </si>
+  <si>
+    <t>0.6665,0.5189,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.6602,0.0061,0.2064,0.0017</t>
+  </si>
+  <si>
+    <t>0.9973,0.0019,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9690,0.0132,0.0095,0.0021</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.9944,0.0024,0.0013,0.0002</t>
+  </si>
+  <si>
+    <t>0.0007,0.0030,0.9959,0.0033</t>
+  </si>
+  <si>
+    <t>0.0000,0.0008,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.7963,0.9931,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0004,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.1978,0.0117,0.6981,0.0043</t>
+  </si>
+  <si>
+    <t>0.2351,0.0019,0.7705,0.0007</t>
+  </si>
+  <si>
+    <t>0.8979,0.0068,0.0573,0.0025</t>
+  </si>
+  <si>
+    <t>0.3568,0.0472,0.3563,0.0005</t>
+  </si>
+  <si>
+    <t>0.0259,0.0180,0.9412,0.0001</t>
+  </si>
+  <si>
+    <t>0.9025,0.0017,0.1317,0.0002</t>
+  </si>
+  <si>
+    <t>0.9279,0.0008,0.0531,0.0018</t>
+  </si>
+  <si>
+    <t>0.0157,0.0024,0.9777,0.0003</t>
+  </si>
+  <si>
+    <t>0.0141,0.9870,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9997,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.3349,0.7835,0.0010,0.0000</t>
+  </si>
+  <si>
+    <t>0.7016,0.4634,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0070,0.9911,0.0007,0.0001</t>
+  </si>
+  <si>
+    <t>0.9934,0.0019,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9972,0.0000,0.0011,0.0000</t>
+  </si>
+  <si>
+    <t>0.9652,0.0003,0.0098,0.0040</t>
+  </si>
+  <si>
+    <t>0.5822,0.0131,0.0808,0.1007</t>
+  </si>
+  <si>
+    <t>0.9384,0.0001,0.0883,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0002,0.9994,0.0009</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9996,0.0001</t>
+  </si>
+  <si>
+    <t>0.0005,0.0613,0.9962,0.0001</t>
+  </si>
+  <si>
+    <t>0.0024,0.0003,0.9962,0.0001</t>
+  </si>
+  <si>
+    <t>0.0011,0.0120,0.9853,0.0006</t>
+  </si>
+  <si>
+    <t>0.9957,0.0031,0.0004,0.0001</t>
+  </si>
+  <si>
+    <t>0.9835,0.0094,0.0016,0.0027</t>
+  </si>
+  <si>
+    <t>0.9972,0.0020,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9980,0.0015,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9980,0.0013,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.0013,0.0015,0.9969,0.0007</t>
+  </si>
+  <si>
+    <t>0.0274,0.2014,0.6499,0.0009</t>
+  </si>
+  <si>
+    <t>0.9781,0.0003,0.0066,0.0033</t>
   </si>
   <si>
     <t>0.0001,0.0002,0.9999,0.0000</t>
   </si>
   <si>
-    <t>0.0149,0.0011,0.9816,0.0003</t>
-  </si>
-  <si>
-    <t>0.0104,0.0012,0.9866,0.0005</t>
-  </si>
-  <si>
-    <t>0.0010,0.0099,0.9951,0.0001</t>
-  </si>
-  <si>
-    <t>0.3744,0.0414,0.3971,0.0002</t>
-  </si>
-  <si>
-    <t>0.0057,0.0042,0.9853,0.0002</t>
-  </si>
-  <si>
-    <t>0.8975,0.0058,0.1022,0.0004</t>
-  </si>
-  <si>
-    <t>0.9240,0.0028,0.0353,0.0017</t>
-  </si>
-  <si>
-    <t>0.0941,0.0125,0.8690,0.0011</t>
-  </si>
-  <si>
-    <t>0.0005,0.9991,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.0003,0.9996,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9655,0.0497,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.8871,0.1839,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0287,0.9753,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9766,0.0053,0.0011,0.0004</t>
-  </si>
-  <si>
-    <t>0.9325,0.0001,0.0536,0.0010</t>
-  </si>
-  <si>
-    <t>0.9561,0.0020,0.0004,0.0074</t>
-  </si>
-  <si>
-    <t>0.9356,0.0020,0.0305,0.0042</t>
-  </si>
-  <si>
-    <t>0.7800,0.0030,0.1662,0.0037</t>
-  </si>
-  <si>
-    <t>0.0006,0.0006,0.9988,0.0009</t>
-  </si>
-  <si>
-    <t>0.0001,0.0016,0.9988,0.0004</t>
-  </si>
-  <si>
-    <t>0.0009,0.0029,0.9958,0.0006</t>
-  </si>
-  <si>
-    <t>0.0010,0.0001,0.9985,0.0000</t>
-  </si>
-  <si>
-    <t>0.0004,0.7156,0.7999,0.0002</t>
-  </si>
-  <si>
-    <t>0.9940,0.0038,0.0005,0.0003</t>
-  </si>
-  <si>
-    <t>0.9656,0.0273,0.0018,0.0018</t>
-  </si>
-  <si>
-    <t>0.9990,0.0005,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9927,0.0066,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9984,0.0007,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0003,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0006,0.9996,0.0013</t>
-  </si>
-  <si>
-    <t>0.0141,0.0640,0.9210,0.0011</t>
-  </si>
-  <si>
-    <t>0.9351,0.0027,0.0235,0.0042</t>
-  </si>
-  <si>
-    <t>0.0004,0.0000,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0012,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0372,0.9969,0.0003</t>
-  </si>
-  <si>
-    <t>0.0084,0.0000,0.9984,0.0000</t>
-  </si>
-  <si>
-    <t>0.0011,0.0002,0.9977,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.0003,0.9987,0.0012</t>
-  </si>
-  <si>
-    <t>0.0012,0.0006,0.9969,0.0002</t>
-  </si>
-  <si>
-    <t>0.9657,0.0017,0.0165,0.0007</t>
-  </si>
-  <si>
-    <t>0.8407,0.0005,0.1051,0.0039</t>
-  </si>
-  <si>
-    <t>0.9957,0.0001,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9983,0.0013,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9977,0.0016,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9992,0.0005,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9942,0.0048,0.0003,0.0001</t>
-  </si>
-  <si>
-    <t>0.9988,0.0003,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0006,0.0009,0.9984,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0006,0.9990,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.5165,0.9967,0.0001</t>
-  </si>
-  <si>
-    <t>0.0013,0.0013,0.9936,0.0032</t>
-  </si>
-  <si>
-    <t>0.0010,0.0000,0.9989,0.0002</t>
-  </si>
-  <si>
-    <t>0.0004,0.0001,0.9928,0.0106</t>
-  </si>
-  <si>
-    <t>0.0366,0.0009,0.9548,0.0016</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.9992,0.0013</t>
-  </si>
-  <si>
-    <t>0.9598,0.0000,0.0004,0.0499</t>
-  </si>
-  <si>
-    <t>0.0006,0.0002,0.0000,0.9998</t>
-  </si>
-  <si>
-    <t>0.0036,0.0000,0.0000,0.9994</t>
-  </si>
-  <si>
-    <t>0.9977,0.0002,0.0000,0.0003</t>
+    <t>0.0001,0.0005,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.6951,0.9936,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0003,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0016,0.0002,0.9979,0.0002</t>
+  </si>
+  <si>
+    <t>0.0014,0.0004,0.9966,0.0005</t>
+  </si>
+  <si>
+    <t>0.0021,0.0043,0.9916,0.0006</t>
+  </si>
+  <si>
+    <t>0.9521,0.0001,0.0278,0.0014</t>
+  </si>
+  <si>
+    <t>0.8008,0.0001,0.1505,0.0022</t>
+  </si>
+  <si>
+    <t>0.9982,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9991,0.0004,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9870,0.0161,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9990,0.0004,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.0032,0.9954,0.0007</t>
+  </si>
+  <si>
+    <t>0.0002,0.0015,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0912,0.9991,0.0002</t>
+  </si>
+  <si>
+    <t>0.0009,0.0011,0.9959,0.0014</t>
+  </si>
+  <si>
+    <t>0.0013,0.0000,0.9987,0.0001</t>
+  </si>
+  <si>
+    <t>0.0052,0.0021,0.8651,0.0589</t>
+  </si>
+  <si>
+    <t>0.9699,0.0003,0.0198,0.0006</t>
+  </si>
+  <si>
+    <t>0.0003,0.0002,0.9987,0.0009</t>
+  </si>
+  <si>
+    <t>0.9538,0.0000,0.0014,0.0317</t>
+  </si>
+  <si>
+    <t>0.0011,0.0003,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.0007,0.0000,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.9967,0.0001,0.0001,0.0006</t>
   </si>
 </sst>
 </file>
@@ -1866,7 +1845,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1880,7 +1859,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1894,7 +1873,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1908,7 +1887,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1922,7 +1901,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1936,7 +1915,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1950,7 +1929,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1964,7 +1943,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1978,7 +1957,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1992,7 +1971,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -2020,7 +1999,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2034,7 +2013,7 @@
         <v>259</v>
       </c>
       <c r="D14" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2048,7 +2027,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2062,7 +2041,7 @@
         <v>261</v>
       </c>
       <c r="D16" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2076,7 +2055,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2090,7 +2069,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>276</v>
+        <v>278</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2104,7 +2083,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>277</v>
+        <v>279</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2118,7 +2097,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>278</v>
+        <v>280</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2132,7 +2111,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2146,7 +2125,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>280</v>
+        <v>282</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2160,7 +2139,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>281</v>
+        <v>283</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2171,10 +2150,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D24" t="s">
-        <v>282</v>
+        <v>284</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2185,10 +2164,10 @@
         <v>259</v>
       </c>
       <c r="C25" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>283</v>
+        <v>285</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2202,7 +2181,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>284</v>
+        <v>286</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2216,7 +2195,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>285</v>
+        <v>287</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2230,7 +2209,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>286</v>
+        <v>288</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2244,7 +2223,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>287</v>
+        <v>289</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2258,7 +2237,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>288</v>
+        <v>290</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2269,10 +2248,10 @@
         <v>259</v>
       </c>
       <c r="C31" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>289</v>
+        <v>291</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2286,7 +2265,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>290</v>
+        <v>292</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2300,7 +2279,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>291</v>
+        <v>293</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2314,7 +2293,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>292</v>
+        <v>294</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2328,7 +2307,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2342,7 +2321,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>294</v>
+        <v>296</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2356,7 +2335,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>295</v>
+        <v>297</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2370,7 +2349,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>296</v>
+        <v>298</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2384,7 +2363,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>297</v>
+        <v>299</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2398,7 +2377,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>298</v>
+        <v>300</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2412,7 +2391,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>299</v>
+        <v>301</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2426,7 +2405,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>300</v>
+        <v>302</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2440,7 +2419,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>301</v>
+        <v>303</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2454,7 +2433,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>302</v>
+        <v>304</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2468,7 +2447,7 @@
         <v>261</v>
       </c>
       <c r="D45" t="s">
-        <v>303</v>
+        <v>305</v>
       </c>
     </row>
     <row r="46" spans="1:4">
@@ -2479,10 +2458,10 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="D46" t="s">
-        <v>304</v>
+        <v>306</v>
       </c>
     </row>
     <row r="47" spans="1:4">
@@ -2496,7 +2475,7 @@
         <v>262</v>
       </c>
       <c r="D47" t="s">
-        <v>305</v>
+        <v>307</v>
       </c>
     </row>
     <row r="48" spans="1:4">
@@ -2510,7 +2489,7 @@
         <v>262</v>
       </c>
       <c r="D48" t="s">
-        <v>306</v>
+        <v>308</v>
       </c>
     </row>
     <row r="49" spans="1:4">
@@ -2524,7 +2503,7 @@
         <v>262</v>
       </c>
       <c r="D49" t="s">
-        <v>307</v>
+        <v>309</v>
       </c>
     </row>
     <row r="50" spans="1:4">
@@ -2538,7 +2517,7 @@
         <v>261</v>
       </c>
       <c r="D50" t="s">
-        <v>308</v>
+        <v>310</v>
       </c>
     </row>
     <row r="51" spans="1:4">
@@ -2552,7 +2531,7 @@
         <v>261</v>
       </c>
       <c r="D51" t="s">
-        <v>309</v>
+        <v>311</v>
       </c>
     </row>
     <row r="52" spans="1:4">
@@ -2566,7 +2545,7 @@
         <v>261</v>
       </c>
       <c r="D52" t="s">
-        <v>310</v>
+        <v>312</v>
       </c>
     </row>
     <row r="53" spans="1:4">
@@ -2580,7 +2559,7 @@
         <v>261</v>
       </c>
       <c r="D53" t="s">
-        <v>311</v>
+        <v>313</v>
       </c>
     </row>
     <row r="54" spans="1:4">
@@ -2594,7 +2573,7 @@
         <v>261</v>
       </c>
       <c r="D54" t="s">
-        <v>312</v>
+        <v>314</v>
       </c>
     </row>
     <row r="55" spans="1:4">
@@ -2608,7 +2587,7 @@
         <v>261</v>
       </c>
       <c r="D55" t="s">
-        <v>313</v>
+        <v>315</v>
       </c>
     </row>
     <row r="56" spans="1:4">
@@ -2622,7 +2601,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>314</v>
+        <v>316</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2636,7 +2615,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>315</v>
+        <v>317</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2650,7 +2629,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>316</v>
+        <v>318</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2664,7 +2643,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>317</v>
+        <v>319</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2678,7 +2657,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>318</v>
+        <v>320</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2692,7 +2671,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>319</v>
+        <v>321</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2706,7 +2685,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>268</v>
+        <v>322</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2720,7 +2699,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2734,7 +2713,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2748,7 +2727,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2762,7 +2741,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2776,7 +2755,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>311</v>
+        <v>327</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2790,7 +2769,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2804,7 +2783,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>325</v>
+        <v>279</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2818,7 +2797,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2832,7 +2811,7 @@
         <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2846,7 +2825,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2860,7 +2839,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2874,7 +2853,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2888,7 +2867,7 @@
         <v>263</v>
       </c>
       <c r="D75" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2902,7 +2881,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2916,7 +2895,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2930,7 +2909,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>265</v>
+        <v>337</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2944,7 +2923,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>334</v>
+        <v>266</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -2958,7 +2937,7 @@
         <v>260</v>
       </c>
       <c r="D80" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="81" spans="1:4">
@@ -2972,7 +2951,7 @@
         <v>260</v>
       </c>
       <c r="D81" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
     </row>
     <row r="82" spans="1:4">
@@ -2986,7 +2965,7 @@
         <v>260</v>
       </c>
       <c r="D82" t="s">
-        <v>265</v>
+        <v>340</v>
       </c>
     </row>
     <row r="83" spans="1:4">
@@ -3000,7 +2979,7 @@
         <v>263</v>
       </c>
       <c r="D83" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="84" spans="1:4">
@@ -3014,7 +2993,7 @@
         <v>263</v>
       </c>
       <c r="D84" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="85" spans="1:4">
@@ -3028,7 +3007,7 @@
         <v>263</v>
       </c>
       <c r="D85" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
     </row>
     <row r="86" spans="1:4">
@@ -3042,7 +3021,7 @@
         <v>263</v>
       </c>
       <c r="D86" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="87" spans="1:4">
@@ -3056,7 +3035,7 @@
         <v>263</v>
       </c>
       <c r="D87" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
     </row>
     <row r="88" spans="1:4">
@@ -3070,7 +3049,7 @@
         <v>263</v>
       </c>
       <c r="D88" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="89" spans="1:4">
@@ -3084,7 +3063,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>318</v>
+        <v>269</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3098,7 +3077,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3112,7 +3091,7 @@
         <v>259</v>
       </c>
       <c r="D91" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
     </row>
     <row r="92" spans="1:4">
@@ -3126,7 +3105,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3140,7 +3119,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3154,7 +3133,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3168,7 +3147,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3182,7 +3161,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3196,7 +3175,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3224,7 +3203,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3238,7 +3217,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3252,7 +3231,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>350</v>
+        <v>272</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3266,7 +3245,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3280,7 +3259,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3294,7 +3273,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3308,7 +3287,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3322,7 +3301,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3336,7 +3315,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3350,7 +3329,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3364,7 +3343,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>357</v>
+        <v>279</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3378,7 +3357,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>358</v>
+        <v>282</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3392,7 +3371,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3406,7 +3385,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>281</v>
+        <v>361</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3420,7 +3399,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>360</v>
+        <v>294</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3434,7 +3413,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>277</v>
+        <v>362</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3448,7 +3427,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>361</v>
+        <v>363</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3459,10 +3438,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D116" t="s">
-        <v>362</v>
+        <v>364</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3473,10 +3452,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D117" t="s">
-        <v>363</v>
+        <v>365</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3490,7 +3469,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>364</v>
+        <v>366</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3501,10 +3480,10 @@
         <v>261</v>
       </c>
       <c r="C119" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>365</v>
+        <v>367</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3518,7 +3497,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>366</v>
+        <v>368</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3532,7 +3511,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>367</v>
+        <v>369</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3546,7 +3525,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>368</v>
+        <v>370</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3560,7 +3539,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>369</v>
+        <v>371</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3574,7 +3553,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>370</v>
+        <v>372</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3588,7 +3567,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3602,7 +3581,7 @@
         <v>262</v>
       </c>
       <c r="D126" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3616,7 +3595,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3630,7 +3609,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>314</v>
+        <v>375</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3644,7 +3623,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>374</v>
+        <v>376</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3658,7 +3637,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>375</v>
+        <v>377</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3672,7 +3651,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>376</v>
+        <v>378</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3686,7 +3665,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3700,7 +3679,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>378</v>
+        <v>380</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3714,7 +3693,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>379</v>
+        <v>381</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3728,7 +3707,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>380</v>
+        <v>382</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3742,7 +3721,7 @@
         <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>381</v>
+        <v>383</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3756,7 +3735,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>382</v>
+        <v>384</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3770,7 +3749,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>383</v>
+        <v>385</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3784,7 +3763,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>384</v>
+        <v>386</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3798,7 +3777,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>385</v>
+        <v>387</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3809,10 +3788,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D141" t="s">
-        <v>386</v>
+        <v>388</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3823,10 +3802,10 @@
         <v>261</v>
       </c>
       <c r="C142" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>387</v>
+        <v>389</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3840,7 +3819,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>388</v>
+        <v>390</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3854,7 +3833,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>389</v>
+        <v>391</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3868,7 +3847,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>334</v>
+        <v>266</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3882,7 +3861,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>334</v>
+        <v>266</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3896,7 +3875,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>334</v>
+        <v>266</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3910,7 +3889,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>390</v>
+        <v>392</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3924,7 +3903,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3938,7 +3917,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>391</v>
+        <v>393</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3952,7 +3931,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>392</v>
+        <v>377</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3963,10 +3942,10 @@
         <v>262</v>
       </c>
       <c r="C152" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3980,7 +3959,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3994,7 +3973,7 @@
         <v>259</v>
       </c>
       <c r="D154" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -4008,7 +3987,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4022,7 +4001,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4036,7 +4015,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4050,7 +4029,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4064,7 +4043,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4078,7 +4057,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>400</v>
+        <v>387</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4148,7 +4127,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>405</v>
+        <v>273</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4162,7 +4141,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4176,7 +4155,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4190,7 +4169,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4204,7 +4183,7 @@
         <v>259</v>
       </c>
       <c r="D169" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
     </row>
     <row r="170" spans="1:4">
@@ -4218,7 +4197,7 @@
         <v>259</v>
       </c>
       <c r="D170" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
     </row>
     <row r="171" spans="1:4">
@@ -4232,7 +4211,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>410</v>
+        <v>272</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4246,7 +4225,7 @@
         <v>259</v>
       </c>
       <c r="D172" t="s">
-        <v>411</v>
+        <v>409</v>
       </c>
     </row>
     <row r="173" spans="1:4">
@@ -4260,7 +4239,7 @@
         <v>259</v>
       </c>
       <c r="D173" t="s">
-        <v>412</v>
+        <v>410</v>
       </c>
     </row>
     <row r="174" spans="1:4">
@@ -4271,10 +4250,10 @@
         <v>259</v>
       </c>
       <c r="C174" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D174" t="s">
-        <v>413</v>
+        <v>411</v>
       </c>
     </row>
     <row r="175" spans="1:4">
@@ -4285,10 +4264,10 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D175" t="s">
-        <v>414</v>
+        <v>412</v>
       </c>
     </row>
     <row r="176" spans="1:4">
@@ -4302,7 +4281,7 @@
         <v>259</v>
       </c>
       <c r="D176" t="s">
-        <v>415</v>
+        <v>413</v>
       </c>
     </row>
     <row r="177" spans="1:4">
@@ -4316,7 +4295,7 @@
         <v>259</v>
       </c>
       <c r="D177" t="s">
-        <v>416</v>
+        <v>414</v>
       </c>
     </row>
     <row r="178" spans="1:4">
@@ -4330,7 +4309,7 @@
         <v>259</v>
       </c>
       <c r="D178" t="s">
-        <v>417</v>
+        <v>415</v>
       </c>
     </row>
     <row r="179" spans="1:4">
@@ -4344,7 +4323,7 @@
         <v>259</v>
       </c>
       <c r="D179" t="s">
-        <v>418</v>
+        <v>416</v>
       </c>
     </row>
     <row r="180" spans="1:4">
@@ -4358,7 +4337,7 @@
         <v>259</v>
       </c>
       <c r="D180" t="s">
-        <v>419</v>
+        <v>417</v>
       </c>
     </row>
     <row r="181" spans="1:4">
@@ -4372,7 +4351,7 @@
         <v>261</v>
       </c>
       <c r="D181" t="s">
-        <v>420</v>
+        <v>418</v>
       </c>
     </row>
     <row r="182" spans="1:4">
@@ -4386,7 +4365,7 @@
         <v>259</v>
       </c>
       <c r="D182" t="s">
-        <v>421</v>
+        <v>419</v>
       </c>
     </row>
     <row r="183" spans="1:4">
@@ -4400,7 +4379,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>422</v>
+        <v>327</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4414,7 +4393,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4428,7 +4407,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4439,10 +4418,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D186" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4456,7 +4435,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4470,7 +4449,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>427</v>
+        <v>327</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4484,7 +4463,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>428</v>
+        <v>289</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4498,7 +4477,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>429</v>
+        <v>424</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4512,7 +4491,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>430</v>
+        <v>425</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4523,10 +4502,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D192" t="s">
-        <v>431</v>
+        <v>426</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4540,7 +4519,7 @@
         <v>259</v>
       </c>
       <c r="D193" t="s">
-        <v>432</v>
+        <v>427</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4554,7 +4533,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>433</v>
+        <v>428</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4568,7 +4547,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>434</v>
+        <v>429</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4582,7 +4561,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>435</v>
+        <v>430</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4596,7 +4575,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>436</v>
+        <v>431</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4610,7 +4589,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>437</v>
+        <v>432</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4624,7 +4603,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>438</v>
+        <v>433</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4635,10 +4614,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D200" t="s">
-        <v>439</v>
+        <v>434</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4652,7 +4631,7 @@
         <v>259</v>
       </c>
       <c r="D201" t="s">
-        <v>440</v>
+        <v>435</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4666,7 +4645,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>441</v>
+        <v>436</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4680,7 +4659,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>442</v>
+        <v>437</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4694,7 +4673,7 @@
         <v>259</v>
       </c>
       <c r="D204" t="s">
-        <v>443</v>
+        <v>438</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4708,7 +4687,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>444</v>
+        <v>439</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4722,7 +4701,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>445</v>
+        <v>440</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4736,7 +4715,7 @@
         <v>259</v>
       </c>
       <c r="D207" t="s">
-        <v>446</v>
+        <v>441</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4750,7 +4729,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>447</v>
+        <v>442</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4764,7 +4743,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>448</v>
+        <v>443</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4778,7 +4757,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>449</v>
+        <v>444</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4792,7 +4771,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>450</v>
+        <v>445</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4803,10 +4782,10 @@
         <v>261</v>
       </c>
       <c r="C212" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4820,7 +4799,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>293</v>
+        <v>272</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4834,7 +4813,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>452</v>
+        <v>447</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4848,7 +4827,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>453</v>
+        <v>448</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4862,7 +4841,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>454</v>
+        <v>270</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4876,7 +4855,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4890,7 +4869,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4904,7 +4883,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4918,7 +4897,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>268</v>
+        <v>273</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4932,7 +4911,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4946,7 +4925,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4960,7 +4939,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4974,7 +4953,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4988,7 +4967,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4999,10 +4978,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="D226" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -5016,7 +4995,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5030,7 +5009,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5044,7 +5023,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>422</v>
+        <v>327</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5058,7 +5037,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5072,7 +5051,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5086,7 +5065,7 @@
         <v>259</v>
       </c>
       <c r="D232" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5100,7 +5079,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5114,7 +5093,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5128,7 +5107,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5142,7 +5121,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5156,7 +5135,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5170,7 +5149,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5184,7 +5163,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>270</v>
+        <v>377</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5198,7 +5177,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5212,7 +5191,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5226,7 +5205,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>476</v>
+        <v>377</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5240,7 +5219,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>477</v>
+        <v>470</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5254,7 +5233,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>478</v>
+        <v>471</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5265,10 +5244,10 @@
         <v>261</v>
       </c>
       <c r="C245" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>479</v>
+        <v>472</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5282,7 +5261,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>480</v>
+        <v>473</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5296,7 +5275,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>481</v>
+        <v>474</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5310,7 +5289,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>482</v>
+        <v>475</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5321,10 +5300,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D249" t="s">
-        <v>483</v>
+        <v>476</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5338,7 +5317,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>484</v>
+        <v>477</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5352,7 +5331,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>485</v>
+        <v>478</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5366,7 +5345,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>486</v>
+        <v>479</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5380,7 +5359,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>487</v>
+        <v>480</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5394,7 +5373,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>334</v>
+        <v>266</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5408,7 +5387,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>334</v>
+        <v>266</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5422,7 +5401,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>488</v>
+        <v>481</v>
       </c>
     </row>
   </sheetData>

--- a/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_120/per_file_predictions_epoch_120.xlsx
+++ b/dataset_agreed/saved_models/baserun/pointcloud_base_run10/epoch_120/per_file_predictions_epoch_120.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="482">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1024" uniqueCount="488">
   <si>
     <t>Filename</t>
   </si>
@@ -808,658 +808,676 @@
     <t>0,1,1,0</t>
   </si>
   <si>
-    <t>0,1,0,1</t>
-  </si>
-  <si>
-    <t>0.9827,0.0033,0.0035,0.0006</t>
+    <t>0,0,0,0</t>
+  </si>
+  <si>
+    <t>1,0,0,1</t>
+  </si>
+  <si>
+    <t>0.9003,0.0153,0.0127,0.0114</t>
+  </si>
+  <si>
+    <t>0.0001,0.0014,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.6874,0.0002,0.0080,0.2427</t>
+  </si>
+  <si>
+    <t>0.0022,0.0000,0.0001,0.9993</t>
+  </si>
+  <si>
+    <t>0.9999,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>1.0000,0.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0008,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.3032,0.0480,0.4695,0.0010</t>
+  </si>
+  <si>
+    <t>0.2018,0.0003,0.8688,0.0002</t>
+  </si>
+  <si>
+    <t>0.7108,0.0010,0.4768,0.0001</t>
+  </si>
+  <si>
+    <t>0.0060,0.0005,0.9927,0.0005</t>
+  </si>
+  <si>
+    <t>0.8681,0.0016,0.0714,0.0018</t>
+  </si>
+  <si>
+    <t>0.0000,0.9998,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0019,0.9963,0.0007,0.0002</t>
+  </si>
+  <si>
+    <t>0.0002,0.9996,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.5192,0.0023,0.3630,0.0063</t>
+  </si>
+  <si>
+    <t>0.0514,0.0001,0.9572,0.0002</t>
+  </si>
+  <si>
+    <t>0.0004,0.0001,0.9991,0.0008</t>
+  </si>
+  <si>
+    <t>0.0038,0.0005,0.9941,0.0002</t>
+  </si>
+  <si>
+    <t>0.0088,0.0000,0.9971,0.0000</t>
+  </si>
+  <si>
+    <t>0.4888,0.0007,0.5507,0.0006</t>
+  </si>
+  <si>
+    <t>0.0018,0.0000,0.9981,0.0003</t>
+  </si>
+  <si>
+    <t>0.0469,0.9654,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.9742,0.0163,0.0050,0.0002</t>
+  </si>
+  <si>
+    <t>0.0003,0.0003,0.9997,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9502,0.0191,0.0007,0.0042</t>
+  </si>
+  <si>
+    <t>0.9612,0.0003,0.0345,0.0004</t>
+  </si>
+  <si>
+    <t>0.3258,0.7425,0.0012,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.9980,0.0236,0.0000</t>
+  </si>
+  <si>
+    <t>0.0164,0.6432,0.1568,0.0025</t>
+  </si>
+  <si>
+    <t>0.0008,0.0039,0.9957,0.0010</t>
+  </si>
+  <si>
+    <t>0.0018,0.0021,0.9922,0.0009</t>
+  </si>
+  <si>
+    <t>0.0028,0.0001,0.9945,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.0012,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0006,0.9995,0.0342</t>
+  </si>
+  <si>
+    <t>0.0003,0.2338,0.0002,0.9984</t>
+  </si>
+  <si>
+    <t>0.0009,0.9953,0.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.0002,0.9993,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.9997,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.9999,0.0006</t>
+  </si>
+  <si>
+    <t>0.0006,0.0029,0.9986,0.0001</t>
+  </si>
+  <si>
+    <t>0.0006,0.0002,0.9983,0.0004</t>
+  </si>
+  <si>
+    <t>0.0004,0.0000,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9998,0.0003</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9989,0.0031</t>
+  </si>
+  <si>
+    <t>0.9985,0.0007,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0003,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0003,0.0009,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0002,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.7739,0.3607,0.0006,0.0000</t>
+  </si>
+  <si>
+    <t>0.9979,0.0013,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9784,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0012,0.9998,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0003,0.9993,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9960,0.9991,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0005</t>
+  </si>
+  <si>
+    <t>0.0023,0.9972,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9942,0.0002,0.0035,0.0001</t>
+  </si>
+  <si>
+    <t>0.0139,0.0006,0.9880,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0069,0.9997,0.0003</t>
+  </si>
+  <si>
+    <t>0.0000,0.9843,0.9872,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9507,0.9994,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9997,0.1585,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9906,0.9938,0.0000</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,0.0007,0.9997</t>
+  </si>
+  <si>
+    <t>0.0000,0.0005,0.0000,1.0000</t>
   </si>
   <si>
     <t>0.0000,0.0000,0.0000,1.0000</t>
   </si>
   <si>
-    <t>0.9216,0.0006,0.0007,0.0559</t>
-  </si>
-  <si>
-    <t>0.0044,0.0000,0.0005,0.9977</t>
-  </si>
-  <si>
-    <t>1.0000,0.0000,0.0000,0.0000</t>
+    <t>0.0002,0.0001,0.0012,0.9995</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.0002,0.9998</t>
+  </si>
+  <si>
+    <t>0.0000,0.0002,0.0000,1.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9955,0.9202,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9989,0.9971,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9749,0.9726,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9974,0.9185,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9979,0.9998,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9993,0.3380,0.0000</t>
   </si>
   <si>
     <t>0.9998,0.0001,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9997,0.0001,0.0000,0.0000</t>
+    <t>0.9851,0.0219,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9975,0.0011,0.0001,0.0003</t>
+  </si>
+  <si>
+    <t>0.9902,0.0118,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9984,0.0006,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9949,0.0055,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0007,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.9998,0.0002</t>
+  </si>
+  <si>
+    <t>0.0001,0.0002,0.9998,0.0001</t>
+  </si>
+  <si>
+    <t>0.9693,0.0009,0.0115,0.0011</t>
+  </si>
+  <si>
+    <t>0.2306,0.0001,0.8247,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.9994,0.0007,0.0000</t>
+  </si>
+  <si>
+    <t>0.0007,0.9987,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,1.0000,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.1664,0.8817,0.0005,0.0001</t>
+  </si>
+  <si>
+    <t>0.9658,0.0004,0.0171,0.0011</t>
+  </si>
+  <si>
+    <t>0.3982,0.0000,0.6347,0.0004</t>
+  </si>
+  <si>
+    <t>0.7371,0.0087,0.0748,0.0146</t>
+  </si>
+  <si>
+    <t>0.9885,0.0002,0.0048,0.0006</t>
+  </si>
+  <si>
+    <t>0.0007,0.0342,0.0045,0.9954</t>
+  </si>
+  <si>
+    <t>0.0008,0.9977,0.0015,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.9998,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.9999,0.0001,0.0006</t>
+  </si>
+  <si>
+    <t>0.0000,0.9959,0.9781,0.0000</t>
+  </si>
+  <si>
+    <t>0.7455,0.3440,0.0012,0.0000</t>
+  </si>
+  <si>
+    <t>0.9080,0.1002,0.0017,0.0003</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9997,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0001,0.0002,0.0002</t>
+  </si>
+  <si>
+    <t>0.9994,0.0001,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9992,0.0001,0.0001,0.0003</t>
   </si>
   <si>
     <t>0.9998,0.0000,0.0000,0.0000</t>
   </si>
   <si>
-    <t>0.9999,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.6105,0.0051,0.2821,0.0012</t>
-  </si>
-  <si>
-    <t>0.2108,0.0080,0.7600,0.0005</t>
-  </si>
-  <si>
-    <t>0.0176,0.0068,0.9784,0.0001</t>
-  </si>
-  <si>
-    <t>0.0090,0.0001,0.9904,0.0005</t>
-  </si>
-  <si>
-    <t>0.9922,0.0007,0.0029,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0009,0.9977,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.0364,0.9737,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.2232,0.0003,0.7144,0.0027</t>
-  </si>
-  <si>
-    <t>0.0169,0.0012,0.9651,0.0022</t>
-  </si>
-  <si>
-    <t>0.0003,0.0000,0.9993,0.0003</t>
-  </si>
-  <si>
-    <t>0.0009,0.0002,0.9981,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0006,0.0000,0.9995,0.0001</t>
-  </si>
-  <si>
-    <t>0.1401,0.8993,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.9427,0.0560,0.0047,0.0003</t>
-  </si>
-  <si>
-    <t>0.0001,0.0005,0.9997,0.0015</t>
-  </si>
-  <si>
-    <t>0.0003,0.9995,0.0002,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9946,0.0032,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.0041,0.9940,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9994,0.0058,0.0000</t>
-  </si>
-  <si>
-    <t>0.0090,0.9601,0.0150,0.0007</t>
-  </si>
-  <si>
-    <t>0.0014,0.0003,0.9962,0.0002</t>
-  </si>
-  <si>
-    <t>0.0146,0.0037,0.9607,0.0028</t>
-  </si>
-  <si>
-    <t>0.0011,0.0004,0.9959,0.0003</t>
-  </si>
-  <si>
-    <t>0.0002,0.0001,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9996,0.0006</t>
-  </si>
-  <si>
-    <t>0.0006,0.6455,0.0006,0.9911</t>
-  </si>
-  <si>
-    <t>0.0001,0.9993,0.0000,0.0013</t>
-  </si>
-  <si>
-    <t>0.0001,0.9995,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9998,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.9998,0.0002</t>
-  </si>
-  <si>
-    <t>0.0005,0.0000,0.9996,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0003,1.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9979,0.0019,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9941,0.0012,0.0022,0.0008</t>
-  </si>
-  <si>
-    <t>0.0001,0.0022,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.9994,0.0003,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9942,0.0051,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9995,0.0002,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.8495,0.9982,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.9999,0.0002</t>
-  </si>
-  <si>
-    <t>0.0002,0.0007,0.9989,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.9963,0.9991,0.0000</t>
+    <t>0.0000,0.4835,0.9989,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.9047,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0000,0.0005,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0092,0.0066,0.9814,0.0004</t>
+  </si>
+  <si>
+    <t>0.9983,0.0001,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.7740,0.0009,0.1129,0.0074</t>
+  </si>
+  <si>
+    <t>0.0207,0.0003,0.9850,0.0001</t>
+  </si>
+  <si>
+    <t>0.9642,0.0003,0.0242,0.0010</t>
+  </si>
+  <si>
+    <t>0.0156,0.0001,0.0001,0.9964</t>
+  </si>
+  <si>
+    <t>0.0000,0.9837,0.9794,0.0000</t>
+  </si>
+  <si>
+    <t>0.9995,0.0001,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0052,0.9898,0.0014,0.0023</t>
+  </si>
+  <si>
+    <t>0.0045,0.9963,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9968,0.0000,0.0020,0.0002</t>
+  </si>
+  <si>
+    <t>0.5696,0.0000,0.0003,0.6312</t>
+  </si>
+  <si>
+    <t>0.0005,0.0014,0.9984,0.0026</t>
+  </si>
+  <si>
+    <t>0.9993,0.0000,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9979,0.0001,0.0006,0.0002</t>
+  </si>
+  <si>
+    <t>0.0525,0.9458,0.0033,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0000,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9880,0.0022,0.0026,0.0006</t>
+  </si>
+  <si>
+    <t>0.7360,0.0128,0.0959,0.0015</t>
+  </si>
+  <si>
+    <t>0.5104,0.0222,0.3535,0.0005</t>
+  </si>
+  <si>
+    <t>0.9981,0.0002,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9989,0.0002,0.0002,0.0001</t>
+  </si>
+  <si>
+    <t>0.9996,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9992,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9995,0.0000,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9991,0.0001,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.9983,0.0011,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9634,0.0490,0.0005,0.0000</t>
+  </si>
+  <si>
+    <t>0.9625,0.0433,0.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0630,0.0006,0.9462,0.0008</t>
+  </si>
+  <si>
+    <t>0.9872,0.0155,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.9964,0.0007,0.0003,0.0012</t>
+  </si>
+  <si>
+    <t>0.9989,0.0006,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9524,0.0162,0.0203,0.0012</t>
+  </si>
+  <si>
+    <t>0.0003,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.9947,0.0014,0.0017,0.0002</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.0023,0.9994,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0001,0.9999,0.0000</t>
+  </si>
+  <si>
+    <t>0.0002,0.1612,0.9957,0.0001</t>
+  </si>
+  <si>
+    <t>0.0000,0.0004,0.9999,0.0001</t>
   </si>
   <si>
     <t>0.0000,0.0000,1.0000,0.0000</t>
   </si>
   <si>
-    <t>0.0021,0.9965,0.0007,0.0000</t>
-  </si>
-  <si>
-    <t>0.9968,0.0002,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.0285,0.0009,0.9751,0.0004</t>
-  </si>
-  <si>
-    <t>0.0002,0.0113,0.9992,0.0012</t>
-  </si>
-  <si>
-    <t>0.0000,0.9937,0.9983,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.9285,0.9523,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9999,0.8748,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9881,0.9843,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.0000,0.0002,0.9998</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0000,1.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0006,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.0000,0.0011,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.0001,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.0000,0.9984,0.9461,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9990,0.9984,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9609,0.9929,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9536,0.9974,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9547,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.9938,0.9638,0.0000</t>
-  </si>
-  <si>
-    <t>0.9999,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0001,0.0000,0.0002</t>
-  </si>
-  <si>
-    <t>0.9955,0.0026,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.9990,0.0004,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0004,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9987,0.0016,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9985,0.0013,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9992,0.0002,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0003,0.0002,0.9997,0.0001</t>
-  </si>
-  <si>
-    <t>0.0045,0.0015,0.9919,0.0002</t>
-  </si>
-  <si>
-    <t>0.9946,0.0002,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.0147,0.0001,0.9888,0.0002</t>
-  </si>
-  <si>
-    <t>0.0012,0.9970,0.0012,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9997,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.3443,0.7100,0.0008,0.0002</t>
-  </si>
-  <si>
-    <t>0.1681,0.0037,0.7149,0.0043</t>
-  </si>
-  <si>
-    <t>0.8303,0.0003,0.1808,0.0003</t>
-  </si>
-  <si>
-    <t>0.9498,0.0011,0.0190,0.0034</t>
-  </si>
-  <si>
-    <t>0.6548,0.0058,0.1444,0.0129</t>
-  </si>
-  <si>
-    <t>0.0030,0.0254,0.0007,0.9944</t>
-  </si>
-  <si>
-    <t>0.0004,0.9983,0.0037,0.0001</t>
-  </si>
-  <si>
-    <t>0.0001,0.9998,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,1.0000,0.0002,0.0003</t>
-  </si>
-  <si>
-    <t>0.0000,0.9955,0.9939,0.0000</t>
-  </si>
-  <si>
-    <t>0.0808,0.9358,0.0006,0.0001</t>
-  </si>
-  <si>
-    <t>0.9375,0.0850,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0003,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0001</t>
-  </si>
-  <si>
-    <t>0.9989,0.0002,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9994,0.0001,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9993,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9994,0.0000,0.0000,0.0003</t>
-  </si>
-  <si>
-    <t>0.9990,0.0000,0.0001,0.0005</t>
-  </si>
-  <si>
-    <t>0.0000,0.1363,0.9991,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.5495,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0014,0.9997,0.0000</t>
-  </si>
-  <si>
-    <t>0.0008,0.0003,0.9980,0.0001</t>
-  </si>
-  <si>
-    <t>0.9997,0.0000,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.1533,0.0019,0.8658,0.0004</t>
-  </si>
-  <si>
-    <t>0.0417,0.0002,0.9721,0.0001</t>
-  </si>
-  <si>
-    <t>0.7725,0.0013,0.1507,0.0079</t>
-  </si>
-  <si>
-    <t>0.0011,0.0001,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.0000,0.9974,0.8038,0.0000</t>
-  </si>
-  <si>
-    <t>0.0166,0.9765,0.0009,0.0034</t>
-  </si>
-  <si>
-    <t>0.2765,0.8197,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.9935,0.0000,0.0045,0.0002</t>
-  </si>
-  <si>
-    <t>0.5810,0.0001,0.0063,0.3333</t>
-  </si>
-  <si>
-    <t>0.0003,0.0009,0.9987,0.0041</t>
-  </si>
-  <si>
-    <t>0.9935,0.0000,0.0023,0.0011</t>
-  </si>
-  <si>
-    <t>0.9992,0.0000,0.0003,0.0002</t>
-  </si>
-  <si>
-    <t>0.0542,0.9372,0.0065,0.0001</t>
-  </si>
-  <si>
-    <t>0.9826,0.0056,0.0024,0.0006</t>
-  </si>
-  <si>
-    <t>0.4259,0.0437,0.0972,0.0051</t>
-  </si>
-  <si>
-    <t>0.7167,0.0911,0.0814,0.0007</t>
-  </si>
-  <si>
-    <t>0.9945,0.0007,0.0009,0.0001</t>
+    <t>0.0000,0.0003,0.9999,0.0001</t>
+  </si>
+  <si>
+    <t>0.2353,0.0022,0.7462,0.0013</t>
+  </si>
+  <si>
+    <t>0.0300,0.0013,0.9738,0.0003</t>
+  </si>
+  <si>
+    <t>0.0081,0.0047,0.9818,0.0009</t>
+  </si>
+  <si>
+    <t>0.2007,0.2080,0.2181,0.0001</t>
+  </si>
+  <si>
+    <t>0.0105,0.0073,0.9753,0.0002</t>
+  </si>
+  <si>
+    <t>0.9249,0.0023,0.0702,0.0006</t>
+  </si>
+  <si>
+    <t>0.9027,0.0055,0.0195,0.0065</t>
+  </si>
+  <si>
+    <t>0.0055,0.0001,0.9923,0.0004</t>
+  </si>
+  <si>
+    <t>0.0004,0.9991,0.0004,0.0000</t>
+  </si>
+  <si>
+    <t>0.0003,0.9994,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9739,0.0435,0.0003,0.0000</t>
+  </si>
+  <si>
+    <t>0.0679,0.9507,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.0968,0.9204,0.0008,0.0001</t>
+  </si>
+  <si>
+    <t>0.9947,0.0008,0.0003,0.0001</t>
+  </si>
+  <si>
+    <t>0.2774,0.0003,0.7795,0.0003</t>
+  </si>
+  <si>
+    <t>0.9010,0.0010,0.0564,0.0020</t>
+  </si>
+  <si>
+    <t>0.6531,0.0169,0.1789,0.0104</t>
+  </si>
+  <si>
+    <t>0.1281,0.0072,0.7994,0.0019</t>
+  </si>
+  <si>
+    <t>0.0053,0.0005,0.9944,0.0009</t>
+  </si>
+  <si>
+    <t>0.0011,0.0024,0.9945,0.0005</t>
+  </si>
+  <si>
+    <t>0.0096,0.0107,0.9745,0.0008</t>
+  </si>
+  <si>
+    <t>0.0003,0.0007,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.0010,0.0084,0.9907,0.0002</t>
+  </si>
+  <si>
+    <t>0.9998,0.0000,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9928,0.0037,0.0011,0.0004</t>
+  </si>
+  <si>
+    <t>0.9971,0.0006,0.0003,0.0010</t>
+  </si>
+  <si>
+    <t>0.9996,0.0001,0.0001,0.0000</t>
+  </si>
+  <si>
+    <t>0.9939,0.0039,0.0005,0.0003</t>
+  </si>
+  <si>
+    <t>0.9978,0.0010,0.0001,0.0002</t>
+  </si>
+  <si>
+    <t>0.9990,0.0005,0.0001,0.0001</t>
+  </si>
+  <si>
+    <t>0.0030,0.0011,0.9938,0.0009</t>
+  </si>
+  <si>
+    <t>0.0031,0.0154,0.9886,0.0009</t>
+  </si>
+  <si>
+    <t>0.8927,0.0021,0.0418,0.0028</t>
+  </si>
+  <si>
+    <t>0.0018,0.0001,0.9992,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0010,0.9989,0.0001</t>
+  </si>
+  <si>
+    <t>0.0004,0.1105,0.9900,0.0003</t>
+  </si>
+  <si>
+    <t>0.0001,0.0000,1.0000,0.0000</t>
+  </si>
+  <si>
+    <t>0.0004,0.0005,0.9991,0.0000</t>
+  </si>
+  <si>
+    <t>0.0006,0.0004,0.9986,0.0002</t>
+  </si>
+  <si>
+    <t>0.0049,0.0144,0.9800,0.0016</t>
+  </si>
+  <si>
+    <t>0.3806,0.0005,0.5984,0.0009</t>
+  </si>
+  <si>
+    <t>0.9767,0.0005,0.0125,0.0004</t>
+  </si>
+  <si>
+    <t>0.9938,0.0003,0.0011,0.0001</t>
+  </si>
+  <si>
+    <t>0.9994,0.0002,0.0000,0.0001</t>
+  </si>
+  <si>
+    <t>0.9945,0.0034,0.0007,0.0003</t>
+  </si>
+  <si>
+    <t>0.9976,0.0020,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9988,0.0007,0.0002,0.0000</t>
+  </si>
+  <si>
+    <t>0.9989,0.0005,0.0000,0.0000</t>
   </si>
   <si>
     <t>0.9990,0.0002,0.0001,0.0001</t>
   </si>
   <si>
-    <t>0.9997,0.0000,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.9983,0.0002,0.0005,0.0002</t>
-  </si>
-  <si>
-    <t>0.9980,0.0003,0.0004,0.0004</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0001,0.0004</t>
-  </si>
-  <si>
-    <t>0.9956,0.0032,0.0001,0.0001</t>
-  </si>
-  <si>
-    <t>0.8770,0.1816,0.0008,0.0000</t>
-  </si>
-  <si>
-    <t>0.6665,0.5189,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.6602,0.0061,0.2064,0.0017</t>
-  </si>
-  <si>
-    <t>0.9973,0.0019,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9991,0.0001,0.0002,0.0002</t>
-  </si>
-  <si>
-    <t>0.9994,0.0002,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9690,0.0132,0.0095,0.0021</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9999,0.0001</t>
-  </si>
-  <si>
-    <t>0.9944,0.0024,0.0013,0.0002</t>
-  </si>
-  <si>
-    <t>0.0007,0.0030,0.9959,0.0033</t>
-  </si>
-  <si>
-    <t>0.0000,0.0008,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.7963,0.9931,0.0001</t>
-  </si>
-  <si>
-    <t>0.0000,0.0004,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.1978,0.0117,0.6981,0.0043</t>
-  </si>
-  <si>
-    <t>0.2351,0.0019,0.7705,0.0007</t>
-  </si>
-  <si>
-    <t>0.8979,0.0068,0.0573,0.0025</t>
-  </si>
-  <si>
-    <t>0.3568,0.0472,0.3563,0.0005</t>
-  </si>
-  <si>
-    <t>0.0259,0.0180,0.9412,0.0001</t>
-  </si>
-  <si>
-    <t>0.9025,0.0017,0.1317,0.0002</t>
-  </si>
-  <si>
-    <t>0.9279,0.0008,0.0531,0.0018</t>
-  </si>
-  <si>
-    <t>0.0157,0.0024,0.9777,0.0003</t>
-  </si>
-  <si>
-    <t>0.0141,0.9870,0.0005,0.0000</t>
-  </si>
-  <si>
-    <t>0.0002,0.9997,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.3349,0.7835,0.0010,0.0000</t>
-  </si>
-  <si>
-    <t>0.7016,0.4634,0.0003,0.0000</t>
-  </si>
-  <si>
-    <t>0.0070,0.9911,0.0007,0.0001</t>
-  </si>
-  <si>
-    <t>0.9934,0.0019,0.0004,0.0000</t>
-  </si>
-  <si>
-    <t>0.9972,0.0000,0.0011,0.0000</t>
-  </si>
-  <si>
-    <t>0.9652,0.0003,0.0098,0.0040</t>
-  </si>
-  <si>
-    <t>0.5822,0.0131,0.0808,0.1007</t>
-  </si>
-  <si>
-    <t>0.9384,0.0001,0.0883,0.0002</t>
-  </si>
-  <si>
-    <t>0.0003,0.0002,0.9994,0.0009</t>
-  </si>
-  <si>
-    <t>0.0002,0.0002,0.9996,0.0001</t>
-  </si>
-  <si>
-    <t>0.0005,0.0613,0.9962,0.0001</t>
-  </si>
-  <si>
-    <t>0.0024,0.0003,0.9962,0.0001</t>
-  </si>
-  <si>
-    <t>0.0011,0.0120,0.9853,0.0006</t>
-  </si>
-  <si>
-    <t>0.9957,0.0031,0.0004,0.0001</t>
-  </si>
-  <si>
-    <t>0.9835,0.0094,0.0016,0.0027</t>
-  </si>
-  <si>
-    <t>0.9972,0.0020,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.9980,0.0015,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9980,0.0013,0.0002,0.0001</t>
-  </si>
-  <si>
-    <t>0.0013,0.0015,0.9969,0.0007</t>
-  </si>
-  <si>
-    <t>0.0274,0.2014,0.6499,0.0009</t>
-  </si>
-  <si>
-    <t>0.9781,0.0003,0.0066,0.0033</t>
-  </si>
-  <si>
-    <t>0.0001,0.0002,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.0005,0.9998,0.0000</t>
-  </si>
-  <si>
-    <t>0.0001,0.6951,0.9936,0.0001</t>
-  </si>
-  <si>
-    <t>0.0002,0.0003,0.9999,0.0000</t>
-  </si>
-  <si>
-    <t>0.0016,0.0002,0.9979,0.0002</t>
-  </si>
-  <si>
-    <t>0.0014,0.0004,0.9966,0.0005</t>
-  </si>
-  <si>
-    <t>0.0021,0.0043,0.9916,0.0006</t>
-  </si>
-  <si>
-    <t>0.9521,0.0001,0.0278,0.0014</t>
-  </si>
-  <si>
-    <t>0.8008,0.0001,0.1505,0.0022</t>
-  </si>
-  <si>
-    <t>0.9982,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9996,0.0001,0.0000,0.0000</t>
-  </si>
-  <si>
-    <t>0.9991,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9870,0.0161,0.0005,0.0001</t>
-  </si>
-  <si>
-    <t>0.9990,0.0004,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.9995,0.0001,0.0001,0.0000</t>
-  </si>
-  <si>
-    <t>0.0007,0.0032,0.9954,0.0007</t>
-  </si>
-  <si>
-    <t>0.0002,0.0015,0.9995,0.0000</t>
-  </si>
-  <si>
-    <t>0.0000,0.0912,0.9991,0.0002</t>
-  </si>
-  <si>
-    <t>0.0009,0.0011,0.9959,0.0014</t>
-  </si>
-  <si>
-    <t>0.0013,0.0000,0.9987,0.0001</t>
-  </si>
-  <si>
-    <t>0.0052,0.0021,0.8651,0.0589</t>
-  </si>
-  <si>
-    <t>0.9699,0.0003,0.0198,0.0006</t>
-  </si>
-  <si>
-    <t>0.0003,0.0002,0.9987,0.0009</t>
-  </si>
-  <si>
-    <t>0.9538,0.0000,0.0014,0.0317</t>
-  </si>
-  <si>
-    <t>0.0011,0.0003,0.0000,0.9997</t>
-  </si>
-  <si>
-    <t>0.0007,0.0000,0.0000,0.9999</t>
-  </si>
-  <si>
-    <t>0.9967,0.0001,0.0001,0.0006</t>
+    <t>0.0024,0.0052,0.9909,0.0005</t>
+  </si>
+  <si>
+    <t>0.0001,0.0022,0.9992,0.0001</t>
+  </si>
+  <si>
+    <t>0.0001,0.0071,0.9995,0.0000</t>
+  </si>
+  <si>
+    <t>0.0013,0.0084,0.9871,0.0018</t>
+  </si>
+  <si>
+    <t>0.0002,0.0000,0.9997,0.0000</t>
+  </si>
+  <si>
+    <t>0.0005,0.0026,0.9936,0.0071</t>
+  </si>
+  <si>
+    <t>0.0607,0.0015,0.9046,0.0036</t>
+  </si>
+  <si>
+    <t>0.0005,0.0002,0.9981,0.0008</t>
+  </si>
+  <si>
+    <t>0.9410,0.0000,0.0018,0.0398</t>
+  </si>
+  <si>
+    <t>0.0002,0.0002,0.0000,0.9999</t>
+  </si>
+  <si>
+    <t>0.0016,0.0000,0.0000,0.9997</t>
+  </si>
+  <si>
+    <t>0.9941,0.0001,0.0000,0.0017</t>
   </si>
 </sst>
 </file>
@@ -1845,7 +1863,7 @@
         <v>259</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1859,7 +1877,7 @@
         <v>260</v>
       </c>
       <c r="D3" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -1873,7 +1891,7 @@
         <v>259</v>
       </c>
       <c r="D4" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1887,7 +1905,7 @@
         <v>260</v>
       </c>
       <c r="D5" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -1901,7 +1919,7 @@
         <v>259</v>
       </c>
       <c r="D6" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -1915,7 +1933,7 @@
         <v>259</v>
       </c>
       <c r="D7" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -1929,7 +1947,7 @@
         <v>259</v>
       </c>
       <c r="D8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1943,7 +1961,7 @@
         <v>259</v>
       </c>
       <c r="D9" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -1957,7 +1975,7 @@
         <v>259</v>
       </c>
       <c r="D10" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -1971,7 +1989,7 @@
         <v>259</v>
       </c>
       <c r="D11" t="s">
-        <v>272</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -1985,7 +2003,7 @@
         <v>259</v>
       </c>
       <c r="D12" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1999,7 +2017,7 @@
         <v>259</v>
       </c>
       <c r="D13" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -2010,10 +2028,10 @@
         <v>259</v>
       </c>
       <c r="C14" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D14" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -2027,7 +2045,7 @@
         <v>261</v>
       </c>
       <c r="D15" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
     </row>
     <row r="16" spans="1:4">
@@ -2038,10 +2056,10 @@
         <v>261</v>
       </c>
       <c r="C16" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D16" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
     </row>
     <row r="17" spans="1:4">
@@ -2055,7 +2073,7 @@
         <v>261</v>
       </c>
       <c r="D17" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="18" spans="1:4">
@@ -2069,7 +2087,7 @@
         <v>259</v>
       </c>
       <c r="D18" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
     </row>
     <row r="19" spans="1:4">
@@ -2083,7 +2101,7 @@
         <v>262</v>
       </c>
       <c r="D19" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
     </row>
     <row r="20" spans="1:4">
@@ -2097,7 +2115,7 @@
         <v>262</v>
       </c>
       <c r="D20" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="21" spans="1:4">
@@ -2111,7 +2129,7 @@
         <v>262</v>
       </c>
       <c r="D21" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
     </row>
     <row r="22" spans="1:4">
@@ -2125,7 +2143,7 @@
         <v>262</v>
       </c>
       <c r="D22" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
     </row>
     <row r="23" spans="1:4">
@@ -2139,7 +2157,7 @@
         <v>262</v>
       </c>
       <c r="D23" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="24" spans="1:4">
@@ -2150,10 +2168,10 @@
         <v>259</v>
       </c>
       <c r="C24" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D24" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
     </row>
     <row r="25" spans="1:4">
@@ -2167,7 +2185,7 @@
         <v>261</v>
       </c>
       <c r="D25" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
     </row>
     <row r="26" spans="1:4">
@@ -2181,7 +2199,7 @@
         <v>261</v>
       </c>
       <c r="D26" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="27" spans="1:4">
@@ -2195,7 +2213,7 @@
         <v>261</v>
       </c>
       <c r="D27" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
     </row>
     <row r="28" spans="1:4">
@@ -2209,7 +2227,7 @@
         <v>261</v>
       </c>
       <c r="D28" t="s">
-        <v>288</v>
+        <v>289</v>
       </c>
     </row>
     <row r="29" spans="1:4">
@@ -2223,7 +2241,7 @@
         <v>261</v>
       </c>
       <c r="D29" t="s">
-        <v>289</v>
+        <v>290</v>
       </c>
     </row>
     <row r="30" spans="1:4">
@@ -2237,7 +2255,7 @@
         <v>261</v>
       </c>
       <c r="D30" t="s">
-        <v>290</v>
+        <v>291</v>
       </c>
     </row>
     <row r="31" spans="1:4">
@@ -2251,7 +2269,7 @@
         <v>262</v>
       </c>
       <c r="D31" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="32" spans="1:4">
@@ -2265,7 +2283,7 @@
         <v>259</v>
       </c>
       <c r="D32" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
     </row>
     <row r="33" spans="1:4">
@@ -2279,7 +2297,7 @@
         <v>261</v>
       </c>
       <c r="D33" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="34" spans="1:4">
@@ -2293,7 +2311,7 @@
         <v>262</v>
       </c>
       <c r="D34" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="35" spans="1:4">
@@ -2307,7 +2325,7 @@
         <v>259</v>
       </c>
       <c r="D35" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
     </row>
     <row r="36" spans="1:4">
@@ -2321,7 +2339,7 @@
         <v>259</v>
       </c>
       <c r="D36" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
     </row>
     <row r="37" spans="1:4">
@@ -2335,7 +2353,7 @@
         <v>262</v>
       </c>
       <c r="D37" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="38" spans="1:4">
@@ -2349,7 +2367,7 @@
         <v>262</v>
       </c>
       <c r="D38" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="39" spans="1:4">
@@ -2363,7 +2381,7 @@
         <v>262</v>
       </c>
       <c r="D39" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
     </row>
     <row r="40" spans="1:4">
@@ -2377,7 +2395,7 @@
         <v>261</v>
       </c>
       <c r="D40" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="41" spans="1:4">
@@ -2391,7 +2409,7 @@
         <v>261</v>
       </c>
       <c r="D41" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
     </row>
     <row r="42" spans="1:4">
@@ -2405,7 +2423,7 @@
         <v>261</v>
       </c>
       <c r="D42" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
     </row>
     <row r="43" spans="1:4">
@@ -2419,7 +2437,7 @@
         <v>261</v>
       </c>
       <c r="D43" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="44" spans="1:4">
@@ -2433,7 +2451,7 @@
         <v>262</v>
       </c>
       <c r="D44" t="s">
-        <v>304</v>
+        <v>284</v>
       </c>
     </row>
     <row r="45" spans="1:4">
@@ -2458,7 +2476,7 @@
         <v>259</v>
       </c>
       <c r="C46" t="s">
-        <v>264</v>
+        <v>260</v>
       </c>
       <c r="D46" t="s">
         <v>306</v>
@@ -2601,7 +2619,7 @@
         <v>259</v>
       </c>
       <c r="D56" t="s">
-        <v>316</v>
+        <v>270</v>
       </c>
     </row>
     <row r="57" spans="1:4">
@@ -2615,7 +2633,7 @@
         <v>259</v>
       </c>
       <c r="D57" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
     </row>
     <row r="58" spans="1:4">
@@ -2629,7 +2647,7 @@
         <v>259</v>
       </c>
       <c r="D58" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
     </row>
     <row r="59" spans="1:4">
@@ -2643,7 +2661,7 @@
         <v>261</v>
       </c>
       <c r="D59" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
     </row>
     <row r="60" spans="1:4">
@@ -2657,7 +2675,7 @@
         <v>259</v>
       </c>
       <c r="D60" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
     </row>
     <row r="61" spans="1:4">
@@ -2671,7 +2689,7 @@
         <v>259</v>
       </c>
       <c r="D61" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
     </row>
     <row r="62" spans="1:4">
@@ -2685,7 +2703,7 @@
         <v>259</v>
       </c>
       <c r="D62" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="63" spans="1:4">
@@ -2699,7 +2717,7 @@
         <v>263</v>
       </c>
       <c r="D63" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
     </row>
     <row r="64" spans="1:4">
@@ -2713,7 +2731,7 @@
         <v>261</v>
       </c>
       <c r="D64" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
     </row>
     <row r="65" spans="1:4">
@@ -2727,7 +2745,7 @@
         <v>261</v>
       </c>
       <c r="D65" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
     </row>
     <row r="66" spans="1:4">
@@ -2741,7 +2759,7 @@
         <v>263</v>
       </c>
       <c r="D66" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
     </row>
     <row r="67" spans="1:4">
@@ -2755,7 +2773,7 @@
         <v>261</v>
       </c>
       <c r="D67" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
     </row>
     <row r="68" spans="1:4">
@@ -2769,7 +2787,7 @@
         <v>262</v>
       </c>
       <c r="D68" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
     </row>
     <row r="69" spans="1:4">
@@ -2783,7 +2801,7 @@
         <v>262</v>
       </c>
       <c r="D69" t="s">
-        <v>279</v>
+        <v>295</v>
       </c>
     </row>
     <row r="70" spans="1:4">
@@ -2797,7 +2815,7 @@
         <v>259</v>
       </c>
       <c r="D70" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
     </row>
     <row r="71" spans="1:4">
@@ -2811,7 +2829,7 @@
         <v>261</v>
       </c>
       <c r="D71" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
     </row>
     <row r="72" spans="1:4">
@@ -2825,7 +2843,7 @@
         <v>261</v>
       </c>
       <c r="D72" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
     </row>
     <row r="73" spans="1:4">
@@ -2839,7 +2857,7 @@
         <v>263</v>
       </c>
       <c r="D73" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
     </row>
     <row r="74" spans="1:4">
@@ -2853,7 +2871,7 @@
         <v>263</v>
       </c>
       <c r="D74" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
     </row>
     <row r="75" spans="1:4">
@@ -2864,10 +2882,10 @@
         <v>262</v>
       </c>
       <c r="C75" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D75" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
     </row>
     <row r="76" spans="1:4">
@@ -2881,7 +2899,7 @@
         <v>263</v>
       </c>
       <c r="D76" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
     </row>
     <row r="77" spans="1:4">
@@ -2895,7 +2913,7 @@
         <v>260</v>
       </c>
       <c r="D77" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
     </row>
     <row r="78" spans="1:4">
@@ -2909,7 +2927,7 @@
         <v>260</v>
       </c>
       <c r="D78" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
     </row>
     <row r="79" spans="1:4">
@@ -2923,7 +2941,7 @@
         <v>260</v>
       </c>
       <c r="D79" t="s">
-        <v>266</v>
+        <v>337</v>
       </c>
     </row>
     <row r="80" spans="1:4">
@@ -3046,7 +3064,7 @@
         <v>262</v>
       </c>
       <c r="C88" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="D88" t="s">
         <v>346</v>
@@ -3063,7 +3081,7 @@
         <v>259</v>
       </c>
       <c r="D89" t="s">
-        <v>269</v>
+        <v>347</v>
       </c>
     </row>
     <row r="90" spans="1:4">
@@ -3077,7 +3095,7 @@
         <v>259</v>
       </c>
       <c r="D90" t="s">
-        <v>347</v>
+        <v>272</v>
       </c>
     </row>
     <row r="91" spans="1:4">
@@ -3105,7 +3123,7 @@
         <v>259</v>
       </c>
       <c r="D92" t="s">
-        <v>349</v>
+        <v>270</v>
       </c>
     </row>
     <row r="93" spans="1:4">
@@ -3119,7 +3137,7 @@
         <v>259</v>
       </c>
       <c r="D93" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
     </row>
     <row r="94" spans="1:4">
@@ -3133,7 +3151,7 @@
         <v>259</v>
       </c>
       <c r="D94" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="95" spans="1:4">
@@ -3147,7 +3165,7 @@
         <v>259</v>
       </c>
       <c r="D95" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
     </row>
     <row r="96" spans="1:4">
@@ -3161,7 +3179,7 @@
         <v>259</v>
       </c>
       <c r="D96" t="s">
-        <v>353</v>
+        <v>319</v>
       </c>
     </row>
     <row r="97" spans="1:4">
@@ -3175,7 +3193,7 @@
         <v>259</v>
       </c>
       <c r="D97" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="98" spans="1:4">
@@ -3189,7 +3207,7 @@
         <v>259</v>
       </c>
       <c r="D98" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="99" spans="1:4">
@@ -3203,7 +3221,7 @@
         <v>259</v>
       </c>
       <c r="D99" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
     </row>
     <row r="100" spans="1:4">
@@ -3217,7 +3235,7 @@
         <v>259</v>
       </c>
       <c r="D100" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="101" spans="1:4">
@@ -3231,7 +3249,7 @@
         <v>259</v>
       </c>
       <c r="D101" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
     </row>
     <row r="102" spans="1:4">
@@ -3245,7 +3263,7 @@
         <v>259</v>
       </c>
       <c r="D102" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
     </row>
     <row r="103" spans="1:4">
@@ -3259,7 +3277,7 @@
         <v>259</v>
       </c>
       <c r="D103" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
     </row>
     <row r="104" spans="1:4">
@@ -3273,7 +3291,7 @@
         <v>259</v>
       </c>
       <c r="D104" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="105" spans="1:4">
@@ -3287,7 +3305,7 @@
         <v>261</v>
       </c>
       <c r="D105" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
     </row>
     <row r="106" spans="1:4">
@@ -3301,7 +3319,7 @@
         <v>261</v>
       </c>
       <c r="D106" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
     </row>
     <row r="107" spans="1:4">
@@ -3315,7 +3333,7 @@
         <v>259</v>
       </c>
       <c r="D107" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
     </row>
     <row r="108" spans="1:4">
@@ -3329,7 +3347,7 @@
         <v>261</v>
       </c>
       <c r="D108" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
     </row>
     <row r="109" spans="1:4">
@@ -3343,7 +3361,7 @@
         <v>262</v>
       </c>
       <c r="D109" t="s">
-        <v>279</v>
+        <v>281</v>
       </c>
     </row>
     <row r="110" spans="1:4">
@@ -3357,7 +3375,7 @@
         <v>262</v>
       </c>
       <c r="D110" t="s">
-        <v>282</v>
+        <v>358</v>
       </c>
     </row>
     <row r="111" spans="1:4">
@@ -3371,7 +3389,7 @@
         <v>262</v>
       </c>
       <c r="D111" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
     </row>
     <row r="112" spans="1:4">
@@ -3385,7 +3403,7 @@
         <v>262</v>
       </c>
       <c r="D112" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
     </row>
     <row r="113" spans="1:4">
@@ -3399,7 +3417,7 @@
         <v>262</v>
       </c>
       <c r="D113" t="s">
-        <v>294</v>
+        <v>358</v>
       </c>
     </row>
     <row r="114" spans="1:4">
@@ -3413,7 +3431,7 @@
         <v>262</v>
       </c>
       <c r="D114" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
     </row>
     <row r="115" spans="1:4">
@@ -3427,7 +3445,7 @@
         <v>262</v>
       </c>
       <c r="D115" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
     </row>
     <row r="116" spans="1:4">
@@ -3438,10 +3456,10 @@
         <v>259</v>
       </c>
       <c r="C116" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D116" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
     </row>
     <row r="117" spans="1:4">
@@ -3452,10 +3470,10 @@
         <v>261</v>
       </c>
       <c r="C117" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D117" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
     </row>
     <row r="118" spans="1:4">
@@ -3469,7 +3487,7 @@
         <v>259</v>
       </c>
       <c r="D118" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
     </row>
     <row r="119" spans="1:4">
@@ -3483,7 +3501,7 @@
         <v>259</v>
       </c>
       <c r="D119" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
     </row>
     <row r="120" spans="1:4">
@@ -3497,7 +3515,7 @@
         <v>260</v>
       </c>
       <c r="D120" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
     </row>
     <row r="121" spans="1:4">
@@ -3511,7 +3529,7 @@
         <v>262</v>
       </c>
       <c r="D121" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
     </row>
     <row r="122" spans="1:4">
@@ -3525,7 +3543,7 @@
         <v>262</v>
       </c>
       <c r="D122" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
     </row>
     <row r="123" spans="1:4">
@@ -3539,7 +3557,7 @@
         <v>262</v>
       </c>
       <c r="D123" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
     </row>
     <row r="124" spans="1:4">
@@ -3553,7 +3571,7 @@
         <v>263</v>
       </c>
       <c r="D124" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
     </row>
     <row r="125" spans="1:4">
@@ -3567,7 +3585,7 @@
         <v>262</v>
       </c>
       <c r="D125" t="s">
-        <v>370</v>
+        <v>309</v>
       </c>
     </row>
     <row r="126" spans="1:4">
@@ -3578,10 +3596,10 @@
         <v>259</v>
       </c>
       <c r="C126" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D126" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
     </row>
     <row r="127" spans="1:4">
@@ -3595,7 +3613,7 @@
         <v>259</v>
       </c>
       <c r="D127" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
     </row>
     <row r="128" spans="1:4">
@@ -3609,7 +3627,7 @@
         <v>259</v>
       </c>
       <c r="D128" t="s">
-        <v>375</v>
+        <v>347</v>
       </c>
     </row>
     <row r="129" spans="1:4">
@@ -3623,7 +3641,7 @@
         <v>259</v>
       </c>
       <c r="D129" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
     </row>
     <row r="130" spans="1:4">
@@ -3637,7 +3655,7 @@
         <v>259</v>
       </c>
       <c r="D130" t="s">
-        <v>377</v>
+        <v>375</v>
       </c>
     </row>
     <row r="131" spans="1:4">
@@ -3651,7 +3669,7 @@
         <v>259</v>
       </c>
       <c r="D131" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="132" spans="1:4">
@@ -3665,7 +3683,7 @@
         <v>259</v>
       </c>
       <c r="D132" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
     </row>
     <row r="133" spans="1:4">
@@ -3679,7 +3697,7 @@
         <v>259</v>
       </c>
       <c r="D133" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
     </row>
     <row r="134" spans="1:4">
@@ -3693,7 +3711,7 @@
         <v>259</v>
       </c>
       <c r="D134" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
     </row>
     <row r="135" spans="1:4">
@@ -3707,7 +3725,7 @@
         <v>259</v>
       </c>
       <c r="D135" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="136" spans="1:4">
@@ -3721,7 +3739,7 @@
         <v>261</v>
       </c>
       <c r="D136" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
     </row>
     <row r="137" spans="1:4">
@@ -3735,7 +3753,7 @@
         <v>263</v>
       </c>
       <c r="D137" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
     </row>
     <row r="138" spans="1:4">
@@ -3749,7 +3767,7 @@
         <v>261</v>
       </c>
       <c r="D138" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="139" spans="1:4">
@@ -3763,7 +3781,7 @@
         <v>261</v>
       </c>
       <c r="D139" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
     </row>
     <row r="140" spans="1:4">
@@ -3777,7 +3795,7 @@
         <v>259</v>
       </c>
       <c r="D140" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
     </row>
     <row r="141" spans="1:4">
@@ -3788,10 +3806,10 @@
         <v>259</v>
       </c>
       <c r="C141" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="D141" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="142" spans="1:4">
@@ -3805,7 +3823,7 @@
         <v>261</v>
       </c>
       <c r="D142" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
     </row>
     <row r="143" spans="1:4">
@@ -3819,7 +3837,7 @@
         <v>259</v>
       </c>
       <c r="D143" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="144" spans="1:4">
@@ -3833,7 +3851,7 @@
         <v>260</v>
       </c>
       <c r="D144" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
     </row>
     <row r="145" spans="1:4">
@@ -3847,7 +3865,7 @@
         <v>260</v>
       </c>
       <c r="D145" t="s">
-        <v>266</v>
+        <v>337</v>
       </c>
     </row>
     <row r="146" spans="1:4">
@@ -3861,7 +3879,7 @@
         <v>260</v>
       </c>
       <c r="D146" t="s">
-        <v>266</v>
+        <v>337</v>
       </c>
     </row>
     <row r="147" spans="1:4">
@@ -3875,7 +3893,7 @@
         <v>260</v>
       </c>
       <c r="D147" t="s">
-        <v>266</v>
+        <v>337</v>
       </c>
     </row>
     <row r="148" spans="1:4">
@@ -3889,7 +3907,7 @@
         <v>263</v>
       </c>
       <c r="D148" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="149" spans="1:4">
@@ -3903,7 +3921,7 @@
         <v>259</v>
       </c>
       <c r="D149" t="s">
-        <v>273</v>
+        <v>390</v>
       </c>
     </row>
     <row r="150" spans="1:4">
@@ -3917,7 +3935,7 @@
         <v>262</v>
       </c>
       <c r="D150" t="s">
-        <v>393</v>
+        <v>391</v>
       </c>
     </row>
     <row r="151" spans="1:4">
@@ -3931,7 +3949,7 @@
         <v>259</v>
       </c>
       <c r="D151" t="s">
-        <v>377</v>
+        <v>379</v>
       </c>
     </row>
     <row r="152" spans="1:4">
@@ -3945,7 +3963,7 @@
         <v>262</v>
       </c>
       <c r="D152" t="s">
-        <v>394</v>
+        <v>392</v>
       </c>
     </row>
     <row r="153" spans="1:4">
@@ -3959,7 +3977,7 @@
         <v>259</v>
       </c>
       <c r="D153" t="s">
-        <v>395</v>
+        <v>393</v>
       </c>
     </row>
     <row r="154" spans="1:4">
@@ -3970,10 +3988,10 @@
         <v>259</v>
       </c>
       <c r="C154" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="D154" t="s">
-        <v>396</v>
+        <v>394</v>
       </c>
     </row>
     <row r="155" spans="1:4">
@@ -3987,7 +4005,7 @@
         <v>259</v>
       </c>
       <c r="D155" t="s">
-        <v>273</v>
+        <v>379</v>
       </c>
     </row>
     <row r="156" spans="1:4">
@@ -4001,7 +4019,7 @@
         <v>261</v>
       </c>
       <c r="D156" t="s">
-        <v>397</v>
+        <v>395</v>
       </c>
     </row>
     <row r="157" spans="1:4">
@@ -4015,7 +4033,7 @@
         <v>259</v>
       </c>
       <c r="D157" t="s">
-        <v>398</v>
+        <v>396</v>
       </c>
     </row>
     <row r="158" spans="1:4">
@@ -4029,7 +4047,7 @@
         <v>259</v>
       </c>
       <c r="D158" t="s">
-        <v>399</v>
+        <v>397</v>
       </c>
     </row>
     <row r="159" spans="1:4">
@@ -4043,7 +4061,7 @@
         <v>262</v>
       </c>
       <c r="D159" t="s">
-        <v>400</v>
+        <v>398</v>
       </c>
     </row>
     <row r="160" spans="1:4">
@@ -4057,7 +4075,7 @@
         <v>259</v>
       </c>
       <c r="D160" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
     </row>
     <row r="161" spans="1:4">
@@ -4071,7 +4089,7 @@
         <v>259</v>
       </c>
       <c r="D161" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
     </row>
     <row r="162" spans="1:4">
@@ -4085,7 +4103,7 @@
         <v>259</v>
       </c>
       <c r="D162" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
     </row>
     <row r="163" spans="1:4">
@@ -4099,7 +4117,7 @@
         <v>259</v>
       </c>
       <c r="D163" t="s">
-        <v>403</v>
+        <v>402</v>
       </c>
     </row>
     <row r="164" spans="1:4">
@@ -4113,7 +4131,7 @@
         <v>259</v>
       </c>
       <c r="D164" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
     </row>
     <row r="165" spans="1:4">
@@ -4127,7 +4145,7 @@
         <v>259</v>
       </c>
       <c r="D165" t="s">
-        <v>273</v>
+        <v>404</v>
       </c>
     </row>
     <row r="166" spans="1:4">
@@ -4141,7 +4159,7 @@
         <v>259</v>
       </c>
       <c r="D166" t="s">
-        <v>271</v>
+        <v>405</v>
       </c>
     </row>
     <row r="167" spans="1:4">
@@ -4155,7 +4173,7 @@
         <v>259</v>
       </c>
       <c r="D167" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
     </row>
     <row r="168" spans="1:4">
@@ -4169,7 +4187,7 @@
         <v>259</v>
       </c>
       <c r="D168" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
     </row>
     <row r="169" spans="1:4">
@@ -4211,7 +4229,7 @@
         <v>259</v>
       </c>
       <c r="D171" t="s">
-        <v>272</v>
+        <v>374</v>
       </c>
     </row>
     <row r="172" spans="1:4">
@@ -4264,7 +4282,7 @@
         <v>262</v>
       </c>
       <c r="C175" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D175" t="s">
         <v>412</v>
@@ -4278,7 +4296,7 @@
         <v>261</v>
       </c>
       <c r="C176" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D176" t="s">
         <v>413</v>
@@ -4379,7 +4397,7 @@
         <v>261</v>
       </c>
       <c r="D183" t="s">
-        <v>327</v>
+        <v>420</v>
       </c>
     </row>
     <row r="184" spans="1:4">
@@ -4393,7 +4411,7 @@
         <v>261</v>
       </c>
       <c r="D184" t="s">
-        <v>420</v>
+        <v>421</v>
       </c>
     </row>
     <row r="185" spans="1:4">
@@ -4407,7 +4425,7 @@
         <v>261</v>
       </c>
       <c r="D185" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
     </row>
     <row r="186" spans="1:4">
@@ -4418,10 +4436,10 @@
         <v>261</v>
       </c>
       <c r="C186" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D186" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
     </row>
     <row r="187" spans="1:4">
@@ -4435,7 +4453,7 @@
         <v>261</v>
       </c>
       <c r="D187" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
     </row>
     <row r="188" spans="1:4">
@@ -4449,7 +4467,7 @@
         <v>261</v>
       </c>
       <c r="D188" t="s">
-        <v>327</v>
+        <v>425</v>
       </c>
     </row>
     <row r="189" spans="1:4">
@@ -4463,7 +4481,7 @@
         <v>261</v>
       </c>
       <c r="D189" t="s">
-        <v>289</v>
+        <v>426</v>
       </c>
     </row>
     <row r="190" spans="1:4">
@@ -4477,7 +4495,7 @@
         <v>261</v>
       </c>
       <c r="D190" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
     </row>
     <row r="191" spans="1:4">
@@ -4491,7 +4509,7 @@
         <v>261</v>
       </c>
       <c r="D191" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
     </row>
     <row r="192" spans="1:4">
@@ -4502,10 +4520,10 @@
         <v>259</v>
       </c>
       <c r="C192" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D192" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
     </row>
     <row r="193" spans="1:4">
@@ -4516,10 +4534,10 @@
         <v>261</v>
       </c>
       <c r="C193" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D193" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="194" spans="1:4">
@@ -4533,7 +4551,7 @@
         <v>261</v>
       </c>
       <c r="D194" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
     </row>
     <row r="195" spans="1:4">
@@ -4547,7 +4565,7 @@
         <v>259</v>
       </c>
       <c r="D195" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
     </row>
     <row r="196" spans="1:4">
@@ -4561,7 +4579,7 @@
         <v>259</v>
       </c>
       <c r="D196" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
     </row>
     <row r="197" spans="1:4">
@@ -4575,7 +4593,7 @@
         <v>261</v>
       </c>
       <c r="D197" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
     </row>
     <row r="198" spans="1:4">
@@ -4589,7 +4607,7 @@
         <v>262</v>
       </c>
       <c r="D198" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
     </row>
     <row r="199" spans="1:4">
@@ -4603,7 +4621,7 @@
         <v>262</v>
       </c>
       <c r="D199" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
     </row>
     <row r="200" spans="1:4">
@@ -4614,10 +4632,10 @@
         <v>262</v>
       </c>
       <c r="C200" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="D200" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
     </row>
     <row r="201" spans="1:4">
@@ -4628,10 +4646,10 @@
         <v>259</v>
       </c>
       <c r="C201" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
       <c r="D201" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
     </row>
     <row r="202" spans="1:4">
@@ -4645,7 +4663,7 @@
         <v>262</v>
       </c>
       <c r="D202" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
     </row>
     <row r="203" spans="1:4">
@@ -4659,7 +4677,7 @@
         <v>259</v>
       </c>
       <c r="D203" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
     </row>
     <row r="204" spans="1:4">
@@ -4670,10 +4688,10 @@
         <v>259</v>
       </c>
       <c r="C204" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D204" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="205" spans="1:4">
@@ -4687,7 +4705,7 @@
         <v>259</v>
       </c>
       <c r="D205" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
     </row>
     <row r="206" spans="1:4">
@@ -4701,7 +4719,7 @@
         <v>259</v>
       </c>
       <c r="D206" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
     </row>
     <row r="207" spans="1:4">
@@ -4712,10 +4730,10 @@
         <v>259</v>
       </c>
       <c r="C207" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D207" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
     </row>
     <row r="208" spans="1:4">
@@ -4729,7 +4747,7 @@
         <v>261</v>
       </c>
       <c r="D208" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
     </row>
     <row r="209" spans="1:4">
@@ -4743,7 +4761,7 @@
         <v>261</v>
       </c>
       <c r="D209" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
     </row>
     <row r="210" spans="1:4">
@@ -4757,7 +4775,7 @@
         <v>261</v>
       </c>
       <c r="D210" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
     </row>
     <row r="211" spans="1:4">
@@ -4771,7 +4789,7 @@
         <v>261</v>
       </c>
       <c r="D211" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
     </row>
     <row r="212" spans="1:4">
@@ -4785,7 +4803,7 @@
         <v>261</v>
       </c>
       <c r="D212" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="213" spans="1:4">
@@ -4799,7 +4817,7 @@
         <v>259</v>
       </c>
       <c r="D213" t="s">
-        <v>272</v>
+        <v>450</v>
       </c>
     </row>
     <row r="214" spans="1:4">
@@ -4813,7 +4831,7 @@
         <v>259</v>
       </c>
       <c r="D214" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
     </row>
     <row r="215" spans="1:4">
@@ -4827,7 +4845,7 @@
         <v>259</v>
       </c>
       <c r="D215" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
     </row>
     <row r="216" spans="1:4">
@@ -4841,7 +4859,7 @@
         <v>259</v>
       </c>
       <c r="D216" t="s">
-        <v>270</v>
+        <v>453</v>
       </c>
     </row>
     <row r="217" spans="1:4">
@@ -4855,7 +4873,7 @@
         <v>259</v>
       </c>
       <c r="D217" t="s">
-        <v>449</v>
+        <v>454</v>
       </c>
     </row>
     <row r="218" spans="1:4">
@@ -4869,7 +4887,7 @@
         <v>259</v>
       </c>
       <c r="D218" t="s">
-        <v>450</v>
+        <v>455</v>
       </c>
     </row>
     <row r="219" spans="1:4">
@@ -4883,7 +4901,7 @@
         <v>259</v>
       </c>
       <c r="D219" t="s">
-        <v>451</v>
+        <v>456</v>
       </c>
     </row>
     <row r="220" spans="1:4">
@@ -4897,7 +4915,7 @@
         <v>259</v>
       </c>
       <c r="D220" t="s">
-        <v>273</v>
+        <v>450</v>
       </c>
     </row>
     <row r="221" spans="1:4">
@@ -4911,7 +4929,7 @@
         <v>261</v>
       </c>
       <c r="D221" t="s">
-        <v>452</v>
+        <v>457</v>
       </c>
     </row>
     <row r="222" spans="1:4">
@@ -4925,7 +4943,7 @@
         <v>261</v>
       </c>
       <c r="D222" t="s">
-        <v>453</v>
+        <v>458</v>
       </c>
     </row>
     <row r="223" spans="1:4">
@@ -4939,7 +4957,7 @@
         <v>259</v>
       </c>
       <c r="D223" t="s">
-        <v>454</v>
+        <v>459</v>
       </c>
     </row>
     <row r="224" spans="1:4">
@@ -4953,7 +4971,7 @@
         <v>261</v>
       </c>
       <c r="D224" t="s">
-        <v>455</v>
+        <v>460</v>
       </c>
     </row>
     <row r="225" spans="1:4">
@@ -4967,7 +4985,7 @@
         <v>261</v>
       </c>
       <c r="D225" t="s">
-        <v>456</v>
+        <v>461</v>
       </c>
     </row>
     <row r="226" spans="1:4">
@@ -4978,10 +4996,10 @@
         <v>261</v>
       </c>
       <c r="C226" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="D226" t="s">
-        <v>457</v>
+        <v>462</v>
       </c>
     </row>
     <row r="227" spans="1:4">
@@ -4995,7 +5013,7 @@
         <v>261</v>
       </c>
       <c r="D227" t="s">
-        <v>458</v>
+        <v>463</v>
       </c>
     </row>
     <row r="228" spans="1:4">
@@ -5009,7 +5027,7 @@
         <v>261</v>
       </c>
       <c r="D228" t="s">
-        <v>459</v>
+        <v>464</v>
       </c>
     </row>
     <row r="229" spans="1:4">
@@ -5023,7 +5041,7 @@
         <v>261</v>
       </c>
       <c r="D229" t="s">
-        <v>327</v>
+        <v>425</v>
       </c>
     </row>
     <row r="230" spans="1:4">
@@ -5037,7 +5055,7 @@
         <v>261</v>
       </c>
       <c r="D230" t="s">
-        <v>460</v>
+        <v>465</v>
       </c>
     </row>
     <row r="231" spans="1:4">
@@ -5051,7 +5069,7 @@
         <v>261</v>
       </c>
       <c r="D231" t="s">
-        <v>461</v>
+        <v>466</v>
       </c>
     </row>
     <row r="232" spans="1:4">
@@ -5062,10 +5080,10 @@
         <v>259</v>
       </c>
       <c r="C232" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D232" t="s">
-        <v>462</v>
+        <v>467</v>
       </c>
     </row>
     <row r="233" spans="1:4">
@@ -5079,7 +5097,7 @@
         <v>259</v>
       </c>
       <c r="D233" t="s">
-        <v>463</v>
+        <v>468</v>
       </c>
     </row>
     <row r="234" spans="1:4">
@@ -5093,7 +5111,7 @@
         <v>259</v>
       </c>
       <c r="D234" t="s">
-        <v>464</v>
+        <v>469</v>
       </c>
     </row>
     <row r="235" spans="1:4">
@@ -5107,7 +5125,7 @@
         <v>259</v>
       </c>
       <c r="D235" t="s">
-        <v>465</v>
+        <v>470</v>
       </c>
     </row>
     <row r="236" spans="1:4">
@@ -5121,7 +5139,7 @@
         <v>259</v>
       </c>
       <c r="D236" t="s">
-        <v>466</v>
+        <v>471</v>
       </c>
     </row>
     <row r="237" spans="1:4">
@@ -5135,7 +5153,7 @@
         <v>259</v>
       </c>
       <c r="D237" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
     </row>
     <row r="238" spans="1:4">
@@ -5149,7 +5167,7 @@
         <v>259</v>
       </c>
       <c r="D238" t="s">
-        <v>467</v>
+        <v>472</v>
       </c>
     </row>
     <row r="239" spans="1:4">
@@ -5163,7 +5181,7 @@
         <v>259</v>
       </c>
       <c r="D239" t="s">
-        <v>377</v>
+        <v>272</v>
       </c>
     </row>
     <row r="240" spans="1:4">
@@ -5177,7 +5195,7 @@
         <v>259</v>
       </c>
       <c r="D240" t="s">
-        <v>468</v>
+        <v>473</v>
       </c>
     </row>
     <row r="241" spans="1:4">
@@ -5191,7 +5209,7 @@
         <v>259</v>
       </c>
       <c r="D241" t="s">
-        <v>469</v>
+        <v>474</v>
       </c>
     </row>
     <row r="242" spans="1:4">
@@ -5205,7 +5223,7 @@
         <v>259</v>
       </c>
       <c r="D242" t="s">
-        <v>377</v>
+        <v>475</v>
       </c>
     </row>
     <row r="243" spans="1:4">
@@ -5219,7 +5237,7 @@
         <v>261</v>
       </c>
       <c r="D243" t="s">
-        <v>470</v>
+        <v>476</v>
       </c>
     </row>
     <row r="244" spans="1:4">
@@ -5233,7 +5251,7 @@
         <v>261</v>
       </c>
       <c r="D244" t="s">
-        <v>471</v>
+        <v>477</v>
       </c>
     </row>
     <row r="245" spans="1:4">
@@ -5247,7 +5265,7 @@
         <v>261</v>
       </c>
       <c r="D245" t="s">
-        <v>472</v>
+        <v>478</v>
       </c>
     </row>
     <row r="246" spans="1:4">
@@ -5261,7 +5279,7 @@
         <v>261</v>
       </c>
       <c r="D246" t="s">
-        <v>473</v>
+        <v>479</v>
       </c>
     </row>
     <row r="247" spans="1:4">
@@ -5275,7 +5293,7 @@
         <v>261</v>
       </c>
       <c r="D247" t="s">
-        <v>474</v>
+        <v>480</v>
       </c>
     </row>
     <row r="248" spans="1:4">
@@ -5289,7 +5307,7 @@
         <v>261</v>
       </c>
       <c r="D248" t="s">
-        <v>475</v>
+        <v>481</v>
       </c>
     </row>
     <row r="249" spans="1:4">
@@ -5300,10 +5318,10 @@
         <v>261</v>
       </c>
       <c r="C249" t="s">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="D249" t="s">
-        <v>476</v>
+        <v>482</v>
       </c>
     </row>
     <row r="250" spans="1:4">
@@ -5317,7 +5335,7 @@
         <v>261</v>
       </c>
       <c r="D250" t="s">
-        <v>477</v>
+        <v>483</v>
       </c>
     </row>
     <row r="251" spans="1:4">
@@ -5331,7 +5349,7 @@
         <v>259</v>
       </c>
       <c r="D251" t="s">
-        <v>478</v>
+        <v>484</v>
       </c>
     </row>
     <row r="252" spans="1:4">
@@ -5345,7 +5363,7 @@
         <v>260</v>
       </c>
       <c r="D252" t="s">
-        <v>479</v>
+        <v>485</v>
       </c>
     </row>
     <row r="253" spans="1:4">
@@ -5359,7 +5377,7 @@
         <v>260</v>
       </c>
       <c r="D253" t="s">
-        <v>480</v>
+        <v>486</v>
       </c>
     </row>
     <row r="254" spans="1:4">
@@ -5373,7 +5391,7 @@
         <v>260</v>
       </c>
       <c r="D254" t="s">
-        <v>266</v>
+        <v>337</v>
       </c>
     </row>
     <row r="255" spans="1:4">
@@ -5387,7 +5405,7 @@
         <v>260</v>
       </c>
       <c r="D255" t="s">
-        <v>266</v>
+        <v>337</v>
       </c>
     </row>
     <row r="256" spans="1:4">
@@ -5401,7 +5419,7 @@
         <v>259</v>
       </c>
       <c r="D256" t="s">
-        <v>481</v>
+        <v>487</v>
       </c>
     </row>
   </sheetData>
